--- a/C_城内多文明配置表_拜占庭.xlsx
+++ b/C_城内多文明配置表_拜占庭.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\T2_Release_0207\excel\xls\Main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Trunk\common\excel\xls\Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98E1E98E-0D41-4C78-8696-F1E67A2AF360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BA44D08-9703-47F9-BD3F-BE4B112A4F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="669" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2060" yWindow="2520" windowWidth="27970" windowHeight="18030" tabRatio="669" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="默认资源路径配置" sheetId="1" r:id="rId1"/>
@@ -365,7 +365,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="750">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="751">
   <si>
     <t>convert(ResCityMulCivil.proto,table_CityMulCivilDefaultAssetPath,CityMulCivilDefaultAssetPath_c3.pbin)</t>
   </si>
@@ -2669,10 +2669,14 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
+    <t>佣兵营地</t>
+  </si>
+  <si>
     <t>23|0|-55</t>
   </si>
   <si>
-    <t>佣兵营地</t>
+    <t>icon_entityiconm_byzantine.smash</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2755,7 +2759,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2801,12 +2805,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39991454817346722"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2880,10 +2878,10 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2895,13 +2893,13 @@
     <xf numFmtId="49" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2931,14 +2929,14 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2946,7 +2944,7 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2959,7 +2957,7 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2969,16 +2967,16 @@
     <xf numFmtId="49" fontId="6" fillId="5" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="11" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="10" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="12" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="11" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2993,7 +2991,7 @@
     <xf numFmtId="47" fontId="2" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3034,16 +3032,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3055,7 +3044,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3067,86 +3065,6 @@
     <cellStyle name="千位分隔 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
   </cellStyles>
   <dxfs count="91">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3249,11 +3167,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C5700"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3274,6 +3192,26 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3349,11 +3287,71 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4686,21 +4684,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.125" style="11" customWidth="1"/>
+    <col min="1" max="1" width="11.08203125" style="11" customWidth="1"/>
     <col min="2" max="2" width="14.25" style="11" customWidth="1"/>
-    <col min="3" max="3" width="21.375" style="11" customWidth="1"/>
+    <col min="3" max="3" width="21.33203125" style="11" customWidth="1"/>
     <col min="4" max="4" width="9" style="11" customWidth="1"/>
     <col min="5" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -4711,7 +4709,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -4719,7 +4717,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="11">
         <v>1</v>
       </c>
@@ -4730,7 +4728,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
         <v>2</v>
       </c>
@@ -4741,7 +4739,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
         <v>3</v>
       </c>
@@ -4752,7 +4750,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
         <v>4</v>
       </c>
@@ -4763,7 +4761,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
         <v>5</v>
       </c>
@@ -4774,7 +4772,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
         <v>6</v>
       </c>
@@ -4785,7 +4783,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
         <v>7</v>
       </c>
@@ -4806,26 +4804,26 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:U247"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.375" style="35" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" style="35" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="35" customWidth="1"/>
     <col min="3" max="3" width="9" style="11" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="35" customWidth="1"/>
-    <col min="5" max="5" width="14.375" style="35" customWidth="1"/>
+    <col min="4" max="4" width="13.58203125" style="35" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" style="35" customWidth="1"/>
     <col min="6" max="11" width="9" style="35" customWidth="1"/>
-    <col min="12" max="12" width="19.375" style="35" customWidth="1"/>
+    <col min="12" max="12" width="19.33203125" style="35" customWidth="1"/>
     <col min="13" max="13" width="9" style="35" customWidth="1"/>
     <col min="14" max="16384" width="9" style="35"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>373</v>
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" spans="1:15" s="31" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" s="31" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="31" t="s">
         <v>366</v>
       </c>
@@ -4840,7 +4838,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="3" spans="1:15" s="39" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" s="39" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="39" t="s">
         <v>104</v>
       </c>
@@ -4855,7 +4853,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="H4" s="35">
         <v>101</v>
       </c>
@@ -4880,7 +4878,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="H5" s="35">
         <v>101</v>
       </c>
@@ -4905,7 +4903,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="H6" s="35">
         <v>101</v>
       </c>
@@ -4930,7 +4928,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="H7" s="35">
         <v>102</v>
       </c>
@@ -4955,7 +4953,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="H8" s="35">
         <v>102</v>
       </c>
@@ -4980,7 +4978,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="H9" s="35">
         <v>102</v>
       </c>
@@ -5005,7 +5003,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="H10" s="35">
         <v>103</v>
       </c>
@@ -5030,7 +5028,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="H11" s="35">
         <v>103</v>
       </c>
@@ -5055,7 +5053,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="H12" s="35">
         <v>103</v>
       </c>
@@ -5080,7 +5078,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="H13" s="35">
         <v>104</v>
       </c>
@@ -5105,7 +5103,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="H14" s="35">
         <v>104</v>
       </c>
@@ -5130,7 +5128,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="H15" s="35">
         <v>104</v>
       </c>
@@ -5155,7 +5153,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="H16" s="35">
         <v>101</v>
       </c>
@@ -5180,7 +5178,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="17" spans="8:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="8:15" x14ac:dyDescent="0.3">
       <c r="H17" s="35">
         <v>101</v>
       </c>
@@ -5205,7 +5203,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="8:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="8:15" x14ac:dyDescent="0.3">
       <c r="H18" s="35">
         <v>101</v>
       </c>
@@ -5230,7 +5228,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="8:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="8:15" x14ac:dyDescent="0.3">
       <c r="H19" s="35">
         <v>101</v>
       </c>
@@ -5255,7 +5253,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="8:15" x14ac:dyDescent="0.2">
+    <row r="20" spans="8:15" x14ac:dyDescent="0.3">
       <c r="H20" s="35">
         <v>101</v>
       </c>
@@ -5280,7 +5278,7 @@
         <v>61.5</v>
       </c>
     </row>
-    <row r="21" spans="8:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="8:15" x14ac:dyDescent="0.3">
       <c r="H21" s="35">
         <v>101</v>
       </c>
@@ -5305,7 +5303,7 @@
         <v>61.5</v>
       </c>
     </row>
-    <row r="22" spans="8:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="8:15" x14ac:dyDescent="0.3">
       <c r="H22" s="35">
         <v>101</v>
       </c>
@@ -5330,7 +5328,7 @@
         <v>61.5</v>
       </c>
     </row>
-    <row r="23" spans="8:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="8:15" x14ac:dyDescent="0.3">
       <c r="H23" s="35">
         <v>101</v>
       </c>
@@ -5355,7 +5353,7 @@
         <v>61.5</v>
       </c>
     </row>
-    <row r="24" spans="8:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="8:15" x14ac:dyDescent="0.3">
       <c r="H24" s="35">
         <v>101</v>
       </c>
@@ -5380,7 +5378,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="25" spans="8:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="8:15" x14ac:dyDescent="0.3">
       <c r="H25" s="35">
         <v>101</v>
       </c>
@@ -5405,7 +5403,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="8:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="8:15" x14ac:dyDescent="0.3">
       <c r="H26" s="35">
         <v>101</v>
       </c>
@@ -5430,7 +5428,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="8:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="8:15" x14ac:dyDescent="0.3">
       <c r="H27" s="35">
         <v>101</v>
       </c>
@@ -5455,7 +5453,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="28" spans="8:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="8:15" x14ac:dyDescent="0.3">
       <c r="H28" s="35">
         <v>101</v>
       </c>
@@ -5480,7 +5478,7 @@
         <v>64.5</v>
       </c>
     </row>
-    <row r="29" spans="8:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="8:15" x14ac:dyDescent="0.3">
       <c r="H29" s="35">
         <v>101</v>
       </c>
@@ -5505,7 +5503,7 @@
         <v>64.5</v>
       </c>
     </row>
-    <row r="30" spans="8:15" x14ac:dyDescent="0.2">
+    <row r="30" spans="8:15" x14ac:dyDescent="0.3">
       <c r="H30" s="35">
         <v>101</v>
       </c>
@@ -5530,7 +5528,7 @@
         <v>64.5</v>
       </c>
     </row>
-    <row r="31" spans="8:15" x14ac:dyDescent="0.2">
+    <row r="31" spans="8:15" x14ac:dyDescent="0.3">
       <c r="H31" s="35">
         <v>101</v>
       </c>
@@ -5555,7 +5553,7 @@
         <v>64.5</v>
       </c>
     </row>
-    <row r="32" spans="8:15" x14ac:dyDescent="0.2">
+    <row r="32" spans="8:15" x14ac:dyDescent="0.3">
       <c r="H32" s="35">
         <v>101</v>
       </c>
@@ -5580,7 +5578,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="H33" s="35">
         <v>101</v>
       </c>
@@ -5605,7 +5603,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="H34" s="35">
         <v>101</v>
       </c>
@@ -5630,7 +5628,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="H35" s="35">
         <v>101</v>
       </c>
@@ -5655,7 +5653,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="H36" s="35">
         <v>101</v>
       </c>
@@ -5680,7 +5678,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="H37" s="35">
         <v>101</v>
       </c>
@@ -5705,7 +5703,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="H38" s="35">
         <v>101</v>
       </c>
@@ -5730,7 +5728,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="H39" s="35">
         <v>101</v>
       </c>
@@ -5755,7 +5753,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="H40" s="35">
         <v>101</v>
       </c>
@@ -5780,7 +5778,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="H41" s="35">
         <v>101</v>
       </c>
@@ -5805,7 +5803,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="H42" s="35">
         <v>101</v>
       </c>
@@ -5830,7 +5828,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="H43" s="35">
         <v>101</v>
       </c>
@@ -5855,7 +5853,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" s="35">
         <v>102</v>
       </c>
@@ -5869,7 +5867,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" s="35">
         <v>102</v>
       </c>
@@ -5884,7 +5882,7 @@
       </c>
       <c r="J45" s="11"/>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" s="35">
         <v>102</v>
       </c>
@@ -5899,7 +5897,7 @@
       </c>
       <c r="J46" s="11"/>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" s="35">
         <v>102</v>
       </c>
@@ -5914,7 +5912,7 @@
       </c>
       <c r="J47" s="11"/>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" s="35">
         <v>102</v>
       </c>
@@ -5929,7 +5927,7 @@
       </c>
       <c r="J48" s="11"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="35">
         <v>102</v>
       </c>
@@ -5944,7 +5942,7 @@
       </c>
       <c r="J49" s="11"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="35">
         <v>102</v>
       </c>
@@ -5959,7 +5957,7 @@
       </c>
       <c r="J50" s="11"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="35">
         <v>102</v>
       </c>
@@ -5974,7 +5972,7 @@
       </c>
       <c r="J51" s="11"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="35">
         <v>102</v>
       </c>
@@ -5989,7 +5987,7 @@
       </c>
       <c r="J52" s="11"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="35">
         <v>102</v>
       </c>
@@ -6004,7 +6002,7 @@
       </c>
       <c r="J53" s="11"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="35">
         <v>102</v>
       </c>
@@ -6019,7 +6017,7 @@
       </c>
       <c r="J54" s="11"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="35">
         <v>102</v>
       </c>
@@ -6034,7 +6032,7 @@
       </c>
       <c r="J55" s="11"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="35">
         <v>102</v>
       </c>
@@ -6049,7 +6047,7 @@
       </c>
       <c r="J56" s="11"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="35">
         <v>102</v>
       </c>
@@ -6064,7 +6062,7 @@
       </c>
       <c r="J57" s="11"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="35">
         <v>102</v>
       </c>
@@ -6079,7 +6077,7 @@
       </c>
       <c r="J58" s="11"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="35">
         <v>102</v>
       </c>
@@ -6094,7 +6092,7 @@
       </c>
       <c r="J59" s="11"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="35">
         <v>102</v>
       </c>
@@ -6109,7 +6107,7 @@
       </c>
       <c r="J60" s="11"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="35">
         <v>102</v>
       </c>
@@ -6124,7 +6122,7 @@
       </c>
       <c r="J61" s="11"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="35">
         <v>102</v>
       </c>
@@ -6139,7 +6137,7 @@
       </c>
       <c r="J62" s="11"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="35">
         <v>102</v>
       </c>
@@ -6154,7 +6152,7 @@
       </c>
       <c r="J63" s="11"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="35">
         <v>102</v>
       </c>
@@ -6169,7 +6167,7 @@
       </c>
       <c r="J64" s="11"/>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A65" s="35">
         <v>102</v>
       </c>
@@ -6184,7 +6182,7 @@
       </c>
       <c r="J65" s="11"/>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A66" s="35">
         <v>102</v>
       </c>
@@ -6199,7 +6197,7 @@
       </c>
       <c r="J66" s="11"/>
     </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A67" s="35">
         <v>102</v>
       </c>
@@ -6214,7 +6212,7 @@
       </c>
       <c r="J67" s="11"/>
     </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A68" s="35">
         <v>102</v>
       </c>
@@ -6229,7 +6227,7 @@
       </c>
       <c r="J68" s="11"/>
     </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A69" s="35">
         <v>102</v>
       </c>
@@ -6244,7 +6242,7 @@
       </c>
       <c r="J69" s="11"/>
     </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A70" s="35">
         <v>102</v>
       </c>
@@ -6259,7 +6257,7 @@
       </c>
       <c r="J70" s="11"/>
     </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A71" s="35">
         <v>102</v>
       </c>
@@ -6274,7 +6272,7 @@
       </c>
       <c r="J71" s="11"/>
     </row>
-    <row r="72" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
       <c r="I72" s="35"/>
       <c r="J72" s="11"/>
       <c r="K72" s="35"/>
@@ -6283,7 +6281,7 @@
       <c r="S72" s="35"/>
       <c r="U72" s="35"/>
     </row>
-    <row r="73" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
       <c r="H73" s="37">
         <v>103</v>
       </c>
@@ -6307,7 +6305,7 @@
         <v>106.84</v>
       </c>
     </row>
-    <row r="74" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
       <c r="H74" s="37">
         <v>103</v>
       </c>
@@ -6331,7 +6329,7 @@
         <v>106.84</v>
       </c>
     </row>
-    <row r="75" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
       <c r="H75" s="37">
         <v>103</v>
       </c>
@@ -6355,7 +6353,7 @@
         <v>106.84</v>
       </c>
     </row>
-    <row r="76" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
       <c r="H76" s="37">
         <v>103</v>
       </c>
@@ -6379,7 +6377,7 @@
         <v>106.84</v>
       </c>
     </row>
-    <row r="77" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
       <c r="H77" s="37">
         <v>103</v>
       </c>
@@ -6403,7 +6401,7 @@
         <v>109.34</v>
       </c>
     </row>
-    <row r="78" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
       <c r="H78" s="37">
         <v>103</v>
       </c>
@@ -6427,7 +6425,7 @@
         <v>109.34</v>
       </c>
     </row>
-    <row r="79" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
       <c r="H79" s="37">
         <v>103</v>
       </c>
@@ -6451,7 +6449,7 @@
         <v>109.34</v>
       </c>
     </row>
-    <row r="80" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:21" s="37" customFormat="1" x14ac:dyDescent="0.3">
       <c r="H80" s="37">
         <v>103</v>
       </c>
@@ -6475,7 +6473,7 @@
         <v>109.34</v>
       </c>
     </row>
-    <row r="81" spans="8:15" s="37" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="8:15" s="37" customFormat="1" x14ac:dyDescent="0.3">
       <c r="H81" s="37">
         <v>103</v>
       </c>
@@ -6499,7 +6497,7 @@
         <v>111.84</v>
       </c>
     </row>
-    <row r="82" spans="8:15" s="37" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="8:15" s="37" customFormat="1" x14ac:dyDescent="0.3">
       <c r="H82" s="37">
         <v>103</v>
       </c>
@@ -6523,7 +6521,7 @@
         <v>111.84</v>
       </c>
     </row>
-    <row r="83" spans="8:15" s="37" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="8:15" s="37" customFormat="1" x14ac:dyDescent="0.3">
       <c r="H83" s="37">
         <v>103</v>
       </c>
@@ -6547,7 +6545,7 @@
         <v>111.84</v>
       </c>
     </row>
-    <row r="84" spans="8:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="8:15" x14ac:dyDescent="0.3">
       <c r="H84" s="37">
         <v>103</v>
       </c>
@@ -6572,7 +6570,7 @@
         <v>111.84</v>
       </c>
     </row>
-    <row r="85" spans="8:15" x14ac:dyDescent="0.2">
+    <row r="85" spans="8:15" x14ac:dyDescent="0.3">
       <c r="H85" s="35">
         <v>104</v>
       </c>
@@ -6597,7 +6595,7 @@
         <v>45.58</v>
       </c>
     </row>
-    <row r="86" spans="8:15" x14ac:dyDescent="0.2">
+    <row r="86" spans="8:15" x14ac:dyDescent="0.3">
       <c r="H86" s="35">
         <v>104</v>
       </c>
@@ -6622,7 +6620,7 @@
         <v>45.58</v>
       </c>
     </row>
-    <row r="87" spans="8:15" x14ac:dyDescent="0.2">
+    <row r="87" spans="8:15" x14ac:dyDescent="0.3">
       <c r="H87" s="35">
         <v>104</v>
       </c>
@@ -6647,7 +6645,7 @@
         <v>45.58</v>
       </c>
     </row>
-    <row r="88" spans="8:15" x14ac:dyDescent="0.2">
+    <row r="88" spans="8:15" x14ac:dyDescent="0.3">
       <c r="H88" s="35">
         <v>104</v>
       </c>
@@ -6672,7 +6670,7 @@
         <v>45.58</v>
       </c>
     </row>
-    <row r="89" spans="8:15" x14ac:dyDescent="0.2">
+    <row r="89" spans="8:15" x14ac:dyDescent="0.3">
       <c r="H89" s="35">
         <v>104</v>
       </c>
@@ -6697,7 +6695,7 @@
         <v>47.08</v>
       </c>
     </row>
-    <row r="90" spans="8:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="8:15" x14ac:dyDescent="0.3">
       <c r="H90" s="35">
         <v>104</v>
       </c>
@@ -6722,7 +6720,7 @@
         <v>47.08</v>
       </c>
     </row>
-    <row r="91" spans="8:15" x14ac:dyDescent="0.2">
+    <row r="91" spans="8:15" x14ac:dyDescent="0.3">
       <c r="H91" s="35">
         <v>104</v>
       </c>
@@ -6747,7 +6745,7 @@
         <v>47.08</v>
       </c>
     </row>
-    <row r="92" spans="8:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="8:15" x14ac:dyDescent="0.3">
       <c r="H92" s="35">
         <v>104</v>
       </c>
@@ -6772,7 +6770,7 @@
         <v>47.08</v>
       </c>
     </row>
-    <row r="93" spans="8:15" x14ac:dyDescent="0.2">
+    <row r="93" spans="8:15" x14ac:dyDescent="0.3">
       <c r="H93" s="35">
         <v>104</v>
       </c>
@@ -6797,7 +6795,7 @@
         <v>48.58</v>
       </c>
     </row>
-    <row r="94" spans="8:15" x14ac:dyDescent="0.2">
+    <row r="94" spans="8:15" x14ac:dyDescent="0.3">
       <c r="H94" s="35">
         <v>104</v>
       </c>
@@ -6822,7 +6820,7 @@
         <v>48.58</v>
       </c>
     </row>
-    <row r="95" spans="8:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="8:15" x14ac:dyDescent="0.3">
       <c r="H95" s="35">
         <v>104</v>
       </c>
@@ -6847,7 +6845,7 @@
         <v>48.58</v>
       </c>
     </row>
-    <row r="96" spans="8:15" x14ac:dyDescent="0.2">
+    <row r="96" spans="8:15" x14ac:dyDescent="0.3">
       <c r="H96" s="35">
         <v>104</v>
       </c>
@@ -6872,7 +6870,7 @@
         <v>48.58</v>
       </c>
     </row>
-    <row r="97" spans="5:15" x14ac:dyDescent="0.2">
+    <row r="97" spans="5:15" x14ac:dyDescent="0.3">
       <c r="H97" s="35">
         <v>104</v>
       </c>
@@ -6897,7 +6895,7 @@
         <v>50.08</v>
       </c>
     </row>
-    <row r="98" spans="5:15" x14ac:dyDescent="0.2">
+    <row r="98" spans="5:15" x14ac:dyDescent="0.3">
       <c r="H98" s="35">
         <v>104</v>
       </c>
@@ -6922,7 +6920,7 @@
         <v>50.08</v>
       </c>
     </row>
-    <row r="99" spans="5:15" x14ac:dyDescent="0.2">
+    <row r="99" spans="5:15" x14ac:dyDescent="0.3">
       <c r="H99" s="35">
         <v>104</v>
       </c>
@@ -6947,7 +6945,7 @@
         <v>50.08</v>
       </c>
     </row>
-    <row r="100" spans="5:15" x14ac:dyDescent="0.2">
+    <row r="100" spans="5:15" x14ac:dyDescent="0.3">
       <c r="H100" s="35">
         <v>104</v>
       </c>
@@ -6972,7 +6970,7 @@
         <v>50.08</v>
       </c>
     </row>
-    <row r="101" spans="5:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="5:15" x14ac:dyDescent="0.3">
       <c r="H101" s="35">
         <v>104</v>
       </c>
@@ -6997,7 +6995,7 @@
         <v>51.58</v>
       </c>
     </row>
-    <row r="102" spans="5:15" x14ac:dyDescent="0.2">
+    <row r="102" spans="5:15" x14ac:dyDescent="0.3">
       <c r="H102" s="35">
         <v>104</v>
       </c>
@@ -7022,7 +7020,7 @@
         <v>51.58</v>
       </c>
     </row>
-    <row r="103" spans="5:15" x14ac:dyDescent="0.2">
+    <row r="103" spans="5:15" x14ac:dyDescent="0.3">
       <c r="H103" s="35">
         <v>104</v>
       </c>
@@ -7047,7 +7045,7 @@
         <v>51.58</v>
       </c>
     </row>
-    <row r="104" spans="5:15" x14ac:dyDescent="0.2">
+    <row r="104" spans="5:15" x14ac:dyDescent="0.3">
       <c r="H104" s="35">
         <v>104</v>
       </c>
@@ -7072,7 +7070,7 @@
         <v>51.58</v>
       </c>
     </row>
-    <row r="105" spans="5:15" x14ac:dyDescent="0.2">
+    <row r="105" spans="5:15" x14ac:dyDescent="0.3">
       <c r="H105" s="35">
         <v>104</v>
       </c>
@@ -7097,7 +7095,7 @@
         <v>53.08</v>
       </c>
     </row>
-    <row r="106" spans="5:15" x14ac:dyDescent="0.2">
+    <row r="106" spans="5:15" x14ac:dyDescent="0.3">
       <c r="H106" s="35">
         <v>104</v>
       </c>
@@ -7122,7 +7120,7 @@
         <v>53.08</v>
       </c>
     </row>
-    <row r="107" spans="5:15" x14ac:dyDescent="0.2">
+    <row r="107" spans="5:15" x14ac:dyDescent="0.3">
       <c r="H107" s="35">
         <v>104</v>
       </c>
@@ -7147,7 +7145,7 @@
         <v>53.08</v>
       </c>
     </row>
-    <row r="108" spans="5:15" x14ac:dyDescent="0.2">
+    <row r="108" spans="5:15" x14ac:dyDescent="0.3">
       <c r="H108" s="35">
         <v>104</v>
       </c>
@@ -7172,7 +7170,7 @@
         <v>53.08</v>
       </c>
     </row>
-    <row r="109" spans="5:15" x14ac:dyDescent="0.2">
+    <row r="109" spans="5:15" x14ac:dyDescent="0.3">
       <c r="H109" s="35">
         <v>104</v>
       </c>
@@ -7197,7 +7195,7 @@
         <v>54.58</v>
       </c>
     </row>
-    <row r="110" spans="5:15" x14ac:dyDescent="0.2">
+    <row r="110" spans="5:15" x14ac:dyDescent="0.3">
       <c r="H110" s="35">
         <v>104</v>
       </c>
@@ -7222,7 +7220,7 @@
         <v>54.58</v>
       </c>
     </row>
-    <row r="111" spans="5:15" x14ac:dyDescent="0.2">
+    <row r="111" spans="5:15" x14ac:dyDescent="0.3">
       <c r="H111" s="35">
         <v>104</v>
       </c>
@@ -7247,7 +7245,7 @@
         <v>54.58</v>
       </c>
     </row>
-    <row r="112" spans="5:15" x14ac:dyDescent="0.2">
+    <row r="112" spans="5:15" x14ac:dyDescent="0.3">
       <c r="E112" s="38"/>
       <c r="H112" s="35">
         <v>104</v>
@@ -7273,382 +7271,382 @@
         <v>54.58</v>
       </c>
     </row>
-    <row r="114" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="114" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E114" s="38"/>
     </row>
-    <row r="115" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="115" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E115" s="38"/>
     </row>
-    <row r="116" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="116" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E116" s="38"/>
     </row>
-    <row r="117" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="117" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E117" s="38"/>
     </row>
-    <row r="118" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="118" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E118" s="38"/>
     </row>
-    <row r="119" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="119" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E119" s="38"/>
     </row>
-    <row r="120" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="120" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E120" s="38"/>
     </row>
-    <row r="121" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="121" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E121" s="38"/>
     </row>
-    <row r="122" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="122" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E122" s="38"/>
     </row>
-    <row r="123" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="123" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E123" s="38"/>
     </row>
-    <row r="124" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="124" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E124" s="38"/>
     </row>
-    <row r="125" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="125" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E125" s="38"/>
     </row>
-    <row r="126" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="126" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E126" s="38"/>
     </row>
-    <row r="127" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="127" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E127" s="38"/>
     </row>
-    <row r="129" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="129" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E129" s="38"/>
     </row>
-    <row r="130" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="130" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E130" s="38"/>
     </row>
-    <row r="131" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="131" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E131" s="38"/>
     </row>
-    <row r="132" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="132" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E132" s="38"/>
     </row>
-    <row r="133" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="133" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E133" s="38"/>
     </row>
-    <row r="134" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="134" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E134" s="38"/>
     </row>
-    <row r="135" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="135" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E135" s="38"/>
     </row>
-    <row r="136" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="136" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E136" s="38"/>
     </row>
-    <row r="137" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="137" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E137" s="38"/>
     </row>
-    <row r="138" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="138" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E138" s="38"/>
     </row>
-    <row r="139" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="139" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E139" s="38"/>
     </row>
-    <row r="140" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="140" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E140" s="38"/>
     </row>
-    <row r="141" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="141" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E141" s="38"/>
     </row>
-    <row r="142" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="142" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E142" s="38"/>
     </row>
-    <row r="144" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="144" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E144" s="38"/>
     </row>
-    <row r="145" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="145" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E145" s="38"/>
     </row>
-    <row r="146" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="146" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E146" s="38"/>
     </row>
-    <row r="147" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="147" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E147" s="38"/>
     </row>
-    <row r="148" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="148" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E148" s="38"/>
     </row>
-    <row r="149" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="149" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E149" s="38"/>
     </row>
-    <row r="150" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="150" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E150" s="38"/>
     </row>
-    <row r="151" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="151" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E151" s="38"/>
     </row>
-    <row r="152" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="152" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E152" s="38"/>
     </row>
-    <row r="153" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="153" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E153" s="38"/>
     </row>
-    <row r="154" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="154" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E154" s="38"/>
     </row>
-    <row r="155" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="155" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E155" s="38"/>
     </row>
-    <row r="156" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="156" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E156" s="38"/>
     </row>
-    <row r="157" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="157" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E157" s="38"/>
     </row>
-    <row r="159" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="159" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E159" s="38"/>
     </row>
-    <row r="160" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="160" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E160" s="38"/>
     </row>
-    <row r="161" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="161" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E161" s="38"/>
     </row>
-    <row r="162" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="162" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E162" s="38"/>
     </row>
-    <row r="163" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="163" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E163" s="38"/>
     </row>
-    <row r="164" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="164" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E164" s="38"/>
     </row>
-    <row r="165" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="165" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E165" s="38"/>
     </row>
-    <row r="166" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="166" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E166" s="38"/>
     </row>
-    <row r="167" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="167" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E167" s="38"/>
     </row>
-    <row r="168" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="168" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E168" s="38"/>
     </row>
-    <row r="169" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="169" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E169" s="38"/>
     </row>
-    <row r="170" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="170" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E170" s="38"/>
     </row>
-    <row r="171" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="171" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E171" s="38"/>
     </row>
-    <row r="172" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="172" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E172" s="38"/>
     </row>
-    <row r="174" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="174" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E174" s="38"/>
     </row>
-    <row r="175" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="175" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E175" s="38"/>
     </row>
-    <row r="176" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="176" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E176" s="38"/>
     </row>
-    <row r="177" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="177" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E177" s="38"/>
     </row>
-    <row r="178" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="178" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E178" s="38"/>
     </row>
-    <row r="179" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="179" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E179" s="38"/>
     </row>
-    <row r="180" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="180" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E180" s="38"/>
     </row>
-    <row r="181" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="181" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E181" s="38"/>
     </row>
-    <row r="182" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="182" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E182" s="38"/>
     </row>
-    <row r="183" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="183" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E183" s="38"/>
     </row>
-    <row r="184" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="184" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E184" s="38"/>
     </row>
-    <row r="185" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="185" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E185" s="38"/>
     </row>
-    <row r="186" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="186" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E186" s="38"/>
     </row>
-    <row r="187" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="187" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E187" s="38"/>
     </row>
-    <row r="189" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="189" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E189" s="38"/>
     </row>
-    <row r="190" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="190" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E190" s="38"/>
     </row>
-    <row r="191" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="191" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E191" s="38"/>
     </row>
-    <row r="192" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="192" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E192" s="38"/>
     </row>
-    <row r="193" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="193" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E193" s="38"/>
     </row>
-    <row r="194" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="194" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E194" s="38"/>
     </row>
-    <row r="195" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="195" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E195" s="38"/>
     </row>
-    <row r="196" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="196" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E196" s="38"/>
     </row>
-    <row r="197" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="197" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E197" s="38"/>
     </row>
-    <row r="198" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="198" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E198" s="38"/>
     </row>
-    <row r="199" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="199" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E199" s="38"/>
     </row>
-    <row r="200" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="200" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E200" s="38"/>
     </row>
-    <row r="201" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="201" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E201" s="38"/>
     </row>
-    <row r="202" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="202" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E202" s="38"/>
     </row>
-    <row r="204" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="204" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E204" s="38"/>
     </row>
-    <row r="205" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="205" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E205" s="38"/>
     </row>
-    <row r="206" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="206" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E206" s="38"/>
     </row>
-    <row r="207" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="207" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E207" s="38"/>
     </row>
-    <row r="208" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="208" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E208" s="38"/>
     </row>
-    <row r="209" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="209" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E209" s="38"/>
     </row>
-    <row r="210" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="210" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E210" s="38"/>
     </row>
-    <row r="211" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="211" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E211" s="38"/>
     </row>
-    <row r="212" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="212" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E212" s="38"/>
     </row>
-    <row r="213" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="213" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E213" s="38"/>
     </row>
-    <row r="214" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="214" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E214" s="38"/>
     </row>
-    <row r="215" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="215" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E215" s="38"/>
     </row>
-    <row r="216" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="216" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E216" s="38"/>
     </row>
-    <row r="217" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="217" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E217" s="38"/>
     </row>
-    <row r="219" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="219" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E219" s="38"/>
     </row>
-    <row r="220" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="220" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E220" s="38"/>
     </row>
-    <row r="221" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="221" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E221" s="38"/>
     </row>
-    <row r="222" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="222" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E222" s="38"/>
     </row>
-    <row r="223" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="223" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E223" s="38"/>
     </row>
-    <row r="224" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="224" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E224" s="38"/>
     </row>
-    <row r="225" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="225" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E225" s="38"/>
     </row>
-    <row r="226" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="226" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E226" s="38"/>
     </row>
-    <row r="227" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="227" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E227" s="38"/>
     </row>
-    <row r="228" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="228" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E228" s="38"/>
     </row>
-    <row r="229" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="229" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E229" s="38"/>
     </row>
-    <row r="230" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="230" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E230" s="38"/>
     </row>
-    <row r="231" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="231" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E231" s="38"/>
     </row>
-    <row r="232" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="232" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E232" s="38"/>
     </row>
-    <row r="234" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="234" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E234" s="38"/>
     </row>
-    <row r="235" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="235" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E235" s="38"/>
     </row>
-    <row r="236" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="236" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E236" s="38"/>
     </row>
-    <row r="237" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="237" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E237" s="38"/>
     </row>
-    <row r="238" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="238" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E238" s="38"/>
     </row>
-    <row r="239" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="239" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E239" s="38"/>
     </row>
-    <row r="240" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="240" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E240" s="38"/>
     </row>
-    <row r="241" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="241" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E241" s="38"/>
     </row>
-    <row r="242" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="242" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E242" s="38"/>
     </row>
-    <row r="243" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="243" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E243" s="38"/>
     </row>
-    <row r="244" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="244" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E244" s="38"/>
     </row>
-    <row r="245" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="245" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E245" s="38"/>
     </row>
-    <row r="246" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="246" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E246" s="38"/>
     </row>
-    <row r="247" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="247" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E247" s="38"/>
     </row>
   </sheetData>
@@ -7666,24 +7664,24 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:T367"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.625" style="35" customWidth="1"/>
-    <col min="2" max="2" width="9.375" style="35" customWidth="1"/>
-    <col min="3" max="3" width="15.625" style="35" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="35" customWidth="1"/>
+    <col min="1" max="1" width="10.58203125" style="35" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" style="35" customWidth="1"/>
+    <col min="3" max="3" width="15.58203125" style="35" customWidth="1"/>
+    <col min="4" max="4" width="13.58203125" style="35" customWidth="1"/>
     <col min="5" max="5" width="9" style="35" customWidth="1"/>
-    <col min="6" max="6" width="10.375" style="35" customWidth="1"/>
+    <col min="6" max="6" width="10.33203125" style="35" customWidth="1"/>
     <col min="7" max="7" width="9" style="35" customWidth="1"/>
     <col min="8" max="16384" width="9" style="35"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="2" spans="1:17" s="31" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" s="31" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="31" t="s">
         <v>366</v>
       </c>
@@ -7697,7 +7695,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="3" spans="1:17" s="39" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" s="39" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="39" t="s">
         <v>104</v>
       </c>
@@ -7711,7 +7709,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="40">
         <v>101</v>
       </c>
@@ -7745,7 +7743,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="40">
         <v>101</v>
       </c>
@@ -7779,7 +7777,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="40">
         <v>101</v>
       </c>
@@ -7813,7 +7811,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="40">
         <v>102</v>
       </c>
@@ -7847,7 +7845,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="40">
         <v>102</v>
       </c>
@@ -7881,7 +7879,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="40">
         <v>102</v>
       </c>
@@ -7915,7 +7913,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="40">
         <v>103</v>
       </c>
@@ -7949,7 +7947,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="40">
         <v>103</v>
       </c>
@@ -7983,7 +7981,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="40">
         <v>103</v>
       </c>
@@ -8017,7 +8015,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="40">
         <v>104</v>
       </c>
@@ -8051,7 +8049,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="40">
         <v>104</v>
       </c>
@@ -8085,7 +8083,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="40">
         <v>104</v>
       </c>
@@ -8119,7 +8117,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="40">
         <v>101</v>
       </c>
@@ -8163,7 +8161,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="40">
         <v>101</v>
       </c>
@@ -8207,7 +8205,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="40">
         <v>101</v>
       </c>
@@ -8248,7 +8246,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="40">
         <v>101</v>
       </c>
@@ -8289,7 +8287,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="40">
         <v>101</v>
       </c>
@@ -8330,7 +8328,7 @@
         <v>79.5</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="40">
         <v>101</v>
       </c>
@@ -8371,7 +8369,7 @@
         <v>79.5</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="40">
         <v>101</v>
       </c>
@@ -8412,7 +8410,7 @@
         <v>79.5</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="40">
         <v>101</v>
       </c>
@@ -8453,7 +8451,7 @@
         <v>79.5</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="40">
         <v>101</v>
       </c>
@@ -8497,7 +8495,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="40">
         <v>101</v>
       </c>
@@ -8541,7 +8539,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="40">
         <v>101</v>
       </c>
@@ -8582,7 +8580,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="40">
         <v>101</v>
       </c>
@@ -8623,7 +8621,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="40">
         <v>101</v>
       </c>
@@ -8667,7 +8665,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="40">
         <v>101</v>
       </c>
@@ -8711,7 +8709,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="40">
         <v>101</v>
       </c>
@@ -8752,7 +8750,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="40">
         <v>101</v>
       </c>
@@ -8793,7 +8791,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="40">
         <v>101</v>
       </c>
@@ -8834,7 +8832,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="40">
         <v>101</v>
       </c>
@@ -8875,7 +8873,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="40">
         <v>101</v>
       </c>
@@ -8916,7 +8914,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="40">
         <v>101</v>
       </c>
@@ -8957,7 +8955,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="40">
         <v>101</v>
       </c>
@@ -8998,7 +8996,7 @@
         <v>85.5</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A37" s="40">
         <v>101</v>
       </c>
@@ -9039,7 +9037,7 @@
         <v>85.5</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="40">
         <v>101</v>
       </c>
@@ -9080,7 +9078,7 @@
         <v>85.5</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="40">
         <v>101</v>
       </c>
@@ -9121,7 +9119,7 @@
         <v>85.5</v>
       </c>
     </row>
-    <row r="40" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="40">
         <v>101</v>
       </c>
@@ -9168,7 +9166,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="41" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="40">
         <v>101</v>
       </c>
@@ -9212,7 +9210,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="42" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="40">
         <v>101</v>
       </c>
@@ -9256,7 +9254,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="43" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="40">
         <v>101</v>
       </c>
@@ -9300,7 +9298,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="44" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="40">
         <v>101</v>
       </c>
@@ -9344,7 +9342,7 @@
         <v>88.5</v>
       </c>
     </row>
-    <row r="45" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="40">
         <v>101</v>
       </c>
@@ -9388,7 +9386,7 @@
         <v>88.5</v>
       </c>
     </row>
-    <row r="46" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="40">
         <v>101</v>
       </c>
@@ -9432,7 +9430,7 @@
         <v>88.5</v>
       </c>
     </row>
-    <row r="47" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="40">
         <v>101</v>
       </c>
@@ -9473,7 +9471,7 @@
         <v>88.5</v>
       </c>
     </row>
-    <row r="48" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="40">
         <v>101</v>
       </c>
@@ -9514,7 +9512,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="49" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="40">
         <v>101</v>
       </c>
@@ -9555,7 +9553,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="50" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="40">
         <v>101</v>
       </c>
@@ -9596,7 +9594,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="51" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A51" s="40">
         <v>101</v>
       </c>
@@ -9637,7 +9635,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="52" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="40">
         <v>101</v>
       </c>
@@ -9678,7 +9676,7 @@
         <v>91.5</v>
       </c>
     </row>
-    <row r="53" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A53" s="40">
         <v>101</v>
       </c>
@@ -9719,7 +9717,7 @@
         <v>91.5</v>
       </c>
     </row>
-    <row r="54" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="40">
         <v>101</v>
       </c>
@@ -9760,7 +9758,7 @@
         <v>91.5</v>
       </c>
     </row>
-    <row r="55" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="40">
         <v>101</v>
       </c>
@@ -9801,7 +9799,7 @@
         <v>91.5</v>
       </c>
     </row>
-    <row r="56" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A56" s="40">
         <v>101</v>
       </c>
@@ -9842,7 +9840,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="57" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="40">
         <v>101</v>
       </c>
@@ -9883,7 +9881,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="58" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="40">
         <v>101</v>
       </c>
@@ -9924,7 +9922,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="59" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A59" s="40">
         <v>101</v>
       </c>
@@ -9965,7 +9963,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="60" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A60" s="40">
         <v>101</v>
       </c>
@@ -10006,7 +10004,7 @@
         <v>94.5</v>
       </c>
     </row>
-    <row r="61" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="40">
         <v>101</v>
       </c>
@@ -10047,7 +10045,7 @@
         <v>94.5</v>
       </c>
     </row>
-    <row r="62" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A62" s="40">
         <v>101</v>
       </c>
@@ -10088,7 +10086,7 @@
         <v>94.5</v>
       </c>
     </row>
-    <row r="63" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="40">
         <v>101</v>
       </c>
@@ -10129,7 +10127,7 @@
         <v>94.5</v>
       </c>
     </row>
-    <row r="64" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:17" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="40">
         <v>101</v>
       </c>
@@ -10170,7 +10168,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="65" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="40">
         <v>101</v>
       </c>
@@ -10211,7 +10209,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="66" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="40">
         <v>101</v>
       </c>
@@ -10252,7 +10250,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="67" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="40">
         <v>101</v>
       </c>
@@ -10293,7 +10291,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="68" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="40">
         <v>101</v>
       </c>
@@ -10334,7 +10332,7 @@
         <v>97.5</v>
       </c>
     </row>
-    <row r="69" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="40">
         <v>101</v>
       </c>
@@ -10375,7 +10373,7 @@
         <v>97.5</v>
       </c>
     </row>
-    <row r="70" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70" s="40">
         <v>101</v>
       </c>
@@ -10416,7 +10414,7 @@
         <v>97.5</v>
       </c>
     </row>
-    <row r="71" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A71" s="40">
         <v>101</v>
       </c>
@@ -10457,7 +10455,7 @@
         <v>97.5</v>
       </c>
     </row>
-    <row r="72" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A72" s="40">
         <v>103</v>
       </c>
@@ -10507,7 +10505,7 @@
         <v>176.72:-9:80.82</v>
       </c>
     </row>
-    <row r="73" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A73" s="40">
         <v>103</v>
       </c>
@@ -10557,7 +10555,7 @@
         <v>173.72:-9:80.82</v>
       </c>
     </row>
-    <row r="74" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A74" s="40">
         <v>103</v>
       </c>
@@ -10610,7 +10608,7 @@
         <v>170.72:-9:80.82</v>
       </c>
     </row>
-    <row r="75" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A75" s="40">
         <v>103</v>
       </c>
@@ -10661,7 +10659,7 @@
         <v>167.72:-9:80.82</v>
       </c>
     </row>
-    <row r="76" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A76" s="40">
         <v>103</v>
       </c>
@@ -10714,7 +10712,7 @@
         <v>173.72:-9:83.32</v>
       </c>
     </row>
-    <row r="77" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A77" s="40">
         <v>103</v>
       </c>
@@ -10764,7 +10762,7 @@
         <v>170.72:-9:83.32</v>
       </c>
     </row>
-    <row r="78" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A78" s="40">
         <v>103</v>
       </c>
@@ -10814,7 +10812,7 @@
         <v>167.72:-9:83.32</v>
       </c>
     </row>
-    <row r="79" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A79" s="40">
         <v>103</v>
       </c>
@@ -10864,7 +10862,7 @@
         <v>176.72:-9:83.32</v>
       </c>
     </row>
-    <row r="80" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A80" s="40">
         <v>103</v>
       </c>
@@ -10914,7 +10912,7 @@
         <v>176.72:-9:85.82</v>
       </c>
     </row>
-    <row r="81" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A81" s="40">
         <v>103</v>
       </c>
@@ -10964,7 +10962,7 @@
         <v>173.72:-9:85.82</v>
       </c>
     </row>
-    <row r="82" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A82" s="40">
         <v>103</v>
       </c>
@@ -11014,7 +11012,7 @@
         <v>170.72:-9:85.82</v>
       </c>
     </row>
-    <row r="83" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A83" s="40">
         <v>103</v>
       </c>
@@ -11064,7 +11062,7 @@
         <v>167.72:-9:85.82</v>
       </c>
     </row>
-    <row r="84" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A84" s="40">
         <v>103</v>
       </c>
@@ -11114,7 +11112,7 @@
         <v>176.72:-9:90.82</v>
       </c>
     </row>
-    <row r="85" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A85" s="40">
         <v>103</v>
       </c>
@@ -11167,7 +11165,7 @@
         <v>173.72:-9:90.82</v>
       </c>
     </row>
-    <row r="86" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A86" s="40">
         <v>103</v>
       </c>
@@ -11218,7 +11216,7 @@
         <v>170.72:-9:90.82</v>
       </c>
     </row>
-    <row r="87" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A87" s="40">
         <v>103</v>
       </c>
@@ -11271,7 +11269,7 @@
         <v>167.72:-9:90.82</v>
       </c>
     </row>
-    <row r="88" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A88" s="40">
         <v>103</v>
       </c>
@@ -11321,7 +11319,7 @@
         <v>173.72:-9:93.32</v>
       </c>
     </row>
-    <row r="89" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A89" s="40">
         <v>103</v>
       </c>
@@ -11371,7 +11369,7 @@
         <v>170.72:-9:93.32</v>
       </c>
     </row>
-    <row r="90" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A90" s="40">
         <v>103</v>
       </c>
@@ -11421,7 +11419,7 @@
         <v>167.72:-9:93.32</v>
       </c>
     </row>
-    <row r="91" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A91" s="40">
         <v>103</v>
       </c>
@@ -11471,7 +11469,7 @@
         <v>176.72:-9:93.32</v>
       </c>
     </row>
-    <row r="92" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A92" s="40">
         <v>103</v>
       </c>
@@ -11521,7 +11519,7 @@
         <v>173.72:-9:95.82</v>
       </c>
     </row>
-    <row r="93" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A93" s="40">
         <v>103</v>
       </c>
@@ -11571,7 +11569,7 @@
         <v>170.72:-9:95.82</v>
       </c>
     </row>
-    <row r="94" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A94" s="40">
         <v>103</v>
       </c>
@@ -11621,7 +11619,7 @@
         <v>167.72:-9:95.82</v>
       </c>
     </row>
-    <row r="95" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A95" s="40">
         <v>103</v>
       </c>
@@ -11671,7 +11669,7 @@
         <v>176.72:-9:95.82</v>
       </c>
     </row>
-    <row r="96" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A96" s="40">
         <v>103</v>
       </c>
@@ -11708,7 +11706,7 @@
         <v>28.34</v>
       </c>
     </row>
-    <row r="97" spans="1:14" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:14" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A97" s="40">
         <v>103</v>
       </c>
@@ -11745,7 +11743,7 @@
         <v>28.34</v>
       </c>
     </row>
-    <row r="98" spans="1:14" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:14" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A98" s="40">
         <v>103</v>
       </c>
@@ -11782,7 +11780,7 @@
         <v>28.34</v>
       </c>
     </row>
-    <row r="99" spans="1:14" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:14" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A99" s="40">
         <v>103</v>
       </c>
@@ -11816,7 +11814,7 @@
         <v>28.34</v>
       </c>
     </row>
-    <row r="100" spans="1:14" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:14" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A100" s="40">
         <v>103</v>
       </c>
@@ -11850,7 +11848,7 @@
         <v>30.84</v>
       </c>
     </row>
-    <row r="101" spans="1:14" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:14" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A101" s="40">
         <v>103</v>
       </c>
@@ -11887,7 +11885,7 @@
         <v>30.84</v>
       </c>
     </row>
-    <row r="102" spans="1:14" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:14" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A102" s="40">
         <v>103</v>
       </c>
@@ -11924,7 +11922,7 @@
         <v>30.84</v>
       </c>
     </row>
-    <row r="103" spans="1:14" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:14" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A103" s="40">
         <v>103</v>
       </c>
@@ -11958,7 +11956,7 @@
         <v>30.84</v>
       </c>
     </row>
-    <row r="104" spans="1:14" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:14" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A104" s="40">
         <v>103</v>
       </c>
@@ -11992,7 +11990,7 @@
         <v>33.340000000000003</v>
       </c>
     </row>
-    <row r="105" spans="1:14" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:14" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A105" s="40">
         <v>103</v>
       </c>
@@ -12026,7 +12024,7 @@
         <v>33.340000000000003</v>
       </c>
     </row>
-    <row r="106" spans="1:14" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:14" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A106" s="40">
         <v>103</v>
       </c>
@@ -12060,7 +12058,7 @@
         <v>33.340000000000003</v>
       </c>
     </row>
-    <row r="107" spans="1:14" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:14" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A107" s="40">
         <v>103</v>
       </c>
@@ -12094,7 +12092,7 @@
         <v>33.340000000000003</v>
       </c>
     </row>
-    <row r="108" spans="1:14" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:14" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A108" s="40">
         <v>103</v>
       </c>
@@ -12128,7 +12126,7 @@
         <v>38.340000000000003</v>
       </c>
     </row>
-    <row r="109" spans="1:14" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:14" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A109" s="40">
         <v>103</v>
       </c>
@@ -12162,7 +12160,7 @@
         <v>38.340000000000003</v>
       </c>
     </row>
-    <row r="110" spans="1:14" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:14" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A110" s="40">
         <v>103</v>
       </c>
@@ -12196,7 +12194,7 @@
         <v>38.340000000000003</v>
       </c>
     </row>
-    <row r="111" spans="1:14" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:14" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A111" s="40">
         <v>103</v>
       </c>
@@ -12230,7 +12228,7 @@
         <v>38.340000000000003</v>
       </c>
     </row>
-    <row r="112" spans="1:14" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:14" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A112" s="40">
         <v>103</v>
       </c>
@@ -12264,7 +12262,7 @@
         <v>40.840000000000003</v>
       </c>
     </row>
-    <row r="113" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A113" s="40">
         <v>103</v>
       </c>
@@ -12298,7 +12296,7 @@
         <v>40.840000000000003</v>
       </c>
     </row>
-    <row r="114" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A114" s="40">
         <v>103</v>
       </c>
@@ -12332,7 +12330,7 @@
         <v>40.840000000000003</v>
       </c>
     </row>
-    <row r="115" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A115" s="40">
         <v>103</v>
       </c>
@@ -12366,7 +12364,7 @@
         <v>40.840000000000003</v>
       </c>
     </row>
-    <row r="116" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A116" s="40">
         <v>103</v>
       </c>
@@ -12400,7 +12398,7 @@
         <v>43.34</v>
       </c>
     </row>
-    <row r="117" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A117" s="40">
         <v>103</v>
       </c>
@@ -12434,7 +12432,7 @@
         <v>43.34</v>
       </c>
     </row>
-    <row r="118" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A118" s="40">
         <v>103</v>
       </c>
@@ -12468,7 +12466,7 @@
         <v>43.34</v>
       </c>
     </row>
-    <row r="119" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A119" s="40">
         <v>103</v>
       </c>
@@ -12502,7 +12500,7 @@
         <v>43.34</v>
       </c>
     </row>
-    <row r="120" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A120" s="40">
         <v>102</v>
       </c>
@@ -12549,7 +12547,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="121" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A121" s="40">
         <v>102</v>
       </c>
@@ -12596,7 +12594,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="122" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A122" s="40">
         <v>102</v>
       </c>
@@ -12640,7 +12638,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="123" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A123" s="40">
         <v>102</v>
       </c>
@@ -12687,7 +12685,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="124" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A124" s="40">
         <v>102</v>
       </c>
@@ -12734,7 +12732,7 @@
         <v>54.5</v>
       </c>
     </row>
-    <row r="125" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A125" s="40">
         <v>102</v>
       </c>
@@ -12778,7 +12776,7 @@
         <v>54.5</v>
       </c>
     </row>
-    <row r="126" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A126" s="40">
         <v>102</v>
       </c>
@@ -12822,7 +12820,7 @@
         <v>54.5</v>
       </c>
     </row>
-    <row r="127" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A127" s="40">
         <v>102</v>
       </c>
@@ -12866,7 +12864,7 @@
         <v>54.5</v>
       </c>
     </row>
-    <row r="128" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A128" s="40">
         <v>102</v>
       </c>
@@ -12910,7 +12908,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="129" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A129" s="40">
         <v>102</v>
       </c>
@@ -12954,7 +12952,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="130" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A130" s="40">
         <v>102</v>
       </c>
@@ -12998,7 +12996,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="131" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A131" s="40">
         <v>102</v>
       </c>
@@ -13042,7 +13040,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="132" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A132" s="40">
         <v>102</v>
       </c>
@@ -13086,7 +13084,7 @@
         <v>57.5</v>
       </c>
     </row>
-    <row r="133" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A133" s="40">
         <v>102</v>
       </c>
@@ -13130,7 +13128,7 @@
         <v>57.5</v>
       </c>
     </row>
-    <row r="134" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A134" s="40">
         <v>102</v>
       </c>
@@ -13174,7 +13172,7 @@
         <v>57.5</v>
       </c>
     </row>
-    <row r="135" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A135" s="40">
         <v>102</v>
       </c>
@@ -13218,7 +13216,7 @@
         <v>57.5</v>
       </c>
     </row>
-    <row r="136" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A136" s="40">
         <v>102</v>
       </c>
@@ -13262,7 +13260,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="137" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A137" s="40">
         <v>102</v>
       </c>
@@ -13306,7 +13304,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="138" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A138" s="40">
         <v>102</v>
       </c>
@@ -13350,7 +13348,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="139" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A139" s="40">
         <v>102</v>
       </c>
@@ -13394,7 +13392,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="140" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A140" s="40">
         <v>102</v>
       </c>
@@ -13438,7 +13436,7 @@
         <v>60.5</v>
       </c>
     </row>
-    <row r="141" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A141" s="40">
         <v>102</v>
       </c>
@@ -13482,7 +13480,7 @@
         <v>60.5</v>
       </c>
     </row>
-    <row r="142" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A142" s="40">
         <v>102</v>
       </c>
@@ -13526,7 +13524,7 @@
         <v>60.5</v>
       </c>
     </row>
-    <row r="143" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A143" s="40">
         <v>102</v>
       </c>
@@ -13570,7 +13568,7 @@
         <v>60.5</v>
       </c>
     </row>
-    <row r="144" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A144" s="40">
         <v>102</v>
       </c>
@@ -13614,7 +13612,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="145" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A145" s="40">
         <v>102</v>
       </c>
@@ -13658,7 +13656,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="146" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A146" s="40">
         <v>102</v>
       </c>
@@ -13702,7 +13700,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="147" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A147" s="40">
         <v>102</v>
       </c>
@@ -13746,7 +13744,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="148" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A148" s="40">
         <v>102</v>
       </c>
@@ -13790,7 +13788,7 @@
         <v>65.08</v>
       </c>
     </row>
-    <row r="149" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A149" s="40">
         <v>102</v>
       </c>
@@ -13834,7 +13832,7 @@
         <v>65.08</v>
       </c>
     </row>
-    <row r="150" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A150" s="40">
         <v>102</v>
       </c>
@@ -13875,7 +13873,7 @@
         <v>65.08</v>
       </c>
     </row>
-    <row r="151" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A151" s="40">
         <v>102</v>
       </c>
@@ -13916,7 +13914,7 @@
         <v>65.08</v>
       </c>
     </row>
-    <row r="152" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A152" s="40">
         <v>102</v>
       </c>
@@ -13960,7 +13958,7 @@
         <v>66.58</v>
       </c>
     </row>
-    <row r="153" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A153" s="40">
         <v>102</v>
       </c>
@@ -14004,7 +14002,7 @@
         <v>66.58</v>
       </c>
     </row>
-    <row r="154" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A154" s="40">
         <v>102</v>
       </c>
@@ -14045,7 +14043,7 @@
         <v>66.58</v>
       </c>
     </row>
-    <row r="155" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A155" s="40">
         <v>102</v>
       </c>
@@ -14086,7 +14084,7 @@
         <v>66.58</v>
       </c>
     </row>
-    <row r="156" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A156" s="40">
         <v>102</v>
       </c>
@@ -14127,7 +14125,7 @@
         <v>68.08</v>
       </c>
     </row>
-    <row r="157" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A157" s="40">
         <v>102</v>
       </c>
@@ -14168,7 +14166,7 @@
         <v>68.08</v>
       </c>
     </row>
-    <row r="158" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A158" s="40">
         <v>102</v>
       </c>
@@ -14209,7 +14207,7 @@
         <v>68.08</v>
       </c>
     </row>
-    <row r="159" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A159" s="40">
         <v>102</v>
       </c>
@@ -14250,7 +14248,7 @@
         <v>68.08</v>
       </c>
     </row>
-    <row r="160" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A160" s="40">
         <v>102</v>
       </c>
@@ -14291,7 +14289,7 @@
         <v>69.58</v>
       </c>
     </row>
-    <row r="161" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A161" s="40">
         <v>102</v>
       </c>
@@ -14332,7 +14330,7 @@
         <v>69.58</v>
       </c>
     </row>
-    <row r="162" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A162" s="40">
         <v>102</v>
       </c>
@@ -14373,7 +14371,7 @@
         <v>69.58</v>
       </c>
     </row>
-    <row r="163" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A163" s="40">
         <v>102</v>
       </c>
@@ -14414,7 +14412,7 @@
         <v>69.58</v>
       </c>
     </row>
-    <row r="164" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A164" s="40">
         <v>102</v>
       </c>
@@ -14455,7 +14453,7 @@
         <v>71.08</v>
       </c>
     </row>
-    <row r="165" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A165" s="40">
         <v>102</v>
       </c>
@@ -14496,7 +14494,7 @@
         <v>71.08</v>
       </c>
     </row>
-    <row r="166" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A166" s="40">
         <v>102</v>
       </c>
@@ -14537,7 +14535,7 @@
         <v>71.08</v>
       </c>
     </row>
-    <row r="167" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A167" s="40">
         <v>102</v>
       </c>
@@ -14578,7 +14576,7 @@
         <v>71.08</v>
       </c>
     </row>
-    <row r="168" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A168" s="40">
         <v>102</v>
       </c>
@@ -14619,7 +14617,7 @@
         <v>72.58</v>
       </c>
     </row>
-    <row r="169" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A169" s="40">
         <v>102</v>
       </c>
@@ -14660,7 +14658,7 @@
         <v>72.58</v>
       </c>
     </row>
-    <row r="170" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A170" s="40">
         <v>102</v>
       </c>
@@ -14701,7 +14699,7 @@
         <v>72.58</v>
       </c>
     </row>
-    <row r="171" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A171" s="40">
         <v>102</v>
       </c>
@@ -14742,7 +14740,7 @@
         <v>72.58</v>
       </c>
     </row>
-    <row r="172" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A172" s="40">
         <v>102</v>
       </c>
@@ -14783,7 +14781,7 @@
         <v>74.08</v>
       </c>
     </row>
-    <row r="173" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A173" s="40">
         <v>102</v>
       </c>
@@ -14824,7 +14822,7 @@
         <v>74.08</v>
       </c>
     </row>
-    <row r="174" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A174" s="40">
         <v>102</v>
       </c>
@@ -14865,7 +14863,7 @@
         <v>74.08</v>
       </c>
     </row>
-    <row r="175" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A175" s="40">
         <v>102</v>
       </c>
@@ -14906,7 +14904,7 @@
         <v>74.08</v>
       </c>
     </row>
-    <row r="176" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A176" s="40">
         <v>104</v>
       </c>
@@ -14950,7 +14948,7 @@
         <v>77.5</v>
       </c>
     </row>
-    <row r="177" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A177" s="40">
         <v>104</v>
       </c>
@@ -14994,7 +14992,7 @@
         <v>77.5</v>
       </c>
     </row>
-    <row r="178" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A178" s="40">
         <v>104</v>
       </c>
@@ -15035,7 +15033,7 @@
         <v>77.5</v>
       </c>
     </row>
-    <row r="179" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A179" s="40">
         <v>104</v>
       </c>
@@ -15079,7 +15077,7 @@
         <v>77.5</v>
       </c>
     </row>
-    <row r="180" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A180" s="40">
         <v>104</v>
       </c>
@@ -15123,7 +15121,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="181" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A181" s="40">
         <v>104</v>
       </c>
@@ -15164,7 +15162,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="182" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A182" s="40">
         <v>104</v>
       </c>
@@ -15205,7 +15203,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="183" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A183" s="40">
         <v>104</v>
       </c>
@@ -15246,7 +15244,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="184" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A184" s="40">
         <v>104</v>
       </c>
@@ -15287,7 +15285,7 @@
         <v>80.5</v>
       </c>
     </row>
-    <row r="185" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A185" s="40">
         <v>104</v>
       </c>
@@ -15328,7 +15326,7 @@
         <v>80.5</v>
       </c>
     </row>
-    <row r="186" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A186" s="40">
         <v>104</v>
       </c>
@@ -15369,7 +15367,7 @@
         <v>80.5</v>
       </c>
     </row>
-    <row r="187" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A187" s="40">
         <v>104</v>
       </c>
@@ -15410,7 +15408,7 @@
         <v>80.5</v>
       </c>
     </row>
-    <row r="188" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A188" s="40">
         <v>104</v>
       </c>
@@ -15451,7 +15449,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="189" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A189" s="40">
         <v>104</v>
       </c>
@@ -15492,7 +15490,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="190" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A190" s="40">
         <v>104</v>
       </c>
@@ -15533,7 +15531,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="191" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A191" s="40">
         <v>104</v>
       </c>
@@ -15574,7 +15572,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="192" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A192" s="40">
         <v>104</v>
       </c>
@@ -15615,7 +15613,7 @@
         <v>83.5</v>
       </c>
     </row>
-    <row r="193" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A193" s="40">
         <v>104</v>
       </c>
@@ -15656,7 +15654,7 @@
         <v>83.5</v>
       </c>
     </row>
-    <row r="194" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A194" s="40">
         <v>104</v>
       </c>
@@ -15697,7 +15695,7 @@
         <v>83.5</v>
       </c>
     </row>
-    <row r="195" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A195" s="40">
         <v>104</v>
       </c>
@@ -15738,7 +15736,7 @@
         <v>83.5</v>
       </c>
     </row>
-    <row r="196" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A196" s="40">
         <v>104</v>
       </c>
@@ -15779,7 +15777,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="197" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A197" s="40">
         <v>104</v>
       </c>
@@ -15820,7 +15818,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="198" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A198" s="40">
         <v>104</v>
       </c>
@@ -15861,7 +15859,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="199" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A199" s="40">
         <v>104</v>
       </c>
@@ -15902,7 +15900,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="200" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A200" s="40">
         <v>104</v>
       </c>
@@ -15943,7 +15941,7 @@
         <v>86.5</v>
       </c>
     </row>
-    <row r="201" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A201" s="40">
         <v>104</v>
       </c>
@@ -15984,7 +15982,7 @@
         <v>86.5</v>
       </c>
     </row>
-    <row r="202" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A202" s="40">
         <v>104</v>
       </c>
@@ -16025,7 +16023,7 @@
         <v>86.5</v>
       </c>
     </row>
-    <row r="203" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A203" s="40">
         <v>104</v>
       </c>
@@ -16066,7 +16064,7 @@
         <v>86.5</v>
       </c>
     </row>
-    <row r="204" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A204" s="40">
         <v>104</v>
       </c>
@@ -16107,7 +16105,7 @@
         <v>90.5</v>
       </c>
     </row>
-    <row r="205" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A205" s="40">
         <v>104</v>
       </c>
@@ -16148,7 +16146,7 @@
         <v>90.5</v>
       </c>
     </row>
-    <row r="206" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A206" s="40">
         <v>104</v>
       </c>
@@ -16189,7 +16187,7 @@
         <v>90.5</v>
       </c>
     </row>
-    <row r="207" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A207" s="40">
         <v>104</v>
       </c>
@@ -16230,7 +16228,7 @@
         <v>90.5</v>
       </c>
     </row>
-    <row r="208" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A208" s="40">
         <v>104</v>
       </c>
@@ -16271,7 +16269,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="209" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A209" s="40">
         <v>104</v>
       </c>
@@ -16312,7 +16310,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="210" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A210" s="40">
         <v>104</v>
       </c>
@@ -16353,7 +16351,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="211" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A211" s="40">
         <v>104</v>
       </c>
@@ -16394,7 +16392,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="212" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A212" s="40">
         <v>104</v>
       </c>
@@ -16435,7 +16433,7 @@
         <v>93.5</v>
       </c>
     </row>
-    <row r="213" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A213" s="40">
         <v>104</v>
       </c>
@@ -16476,7 +16474,7 @@
         <v>93.5</v>
       </c>
     </row>
-    <row r="214" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A214" s="40">
         <v>104</v>
       </c>
@@ -16517,7 +16515,7 @@
         <v>93.5</v>
       </c>
     </row>
-    <row r="215" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A215" s="40">
         <v>104</v>
       </c>
@@ -16558,7 +16556,7 @@
         <v>93.5</v>
       </c>
     </row>
-    <row r="216" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A216" s="40">
         <v>104</v>
       </c>
@@ -16599,7 +16597,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="217" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A217" s="40">
         <v>104</v>
       </c>
@@ -16640,7 +16638,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="218" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A218" s="40">
         <v>104</v>
       </c>
@@ -16681,7 +16679,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="219" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A219" s="40">
         <v>104</v>
       </c>
@@ -16722,7 +16720,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="220" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A220" s="40">
         <v>104</v>
       </c>
@@ -16763,7 +16761,7 @@
         <v>96.5</v>
       </c>
     </row>
-    <row r="221" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A221" s="40">
         <v>104</v>
       </c>
@@ -16804,7 +16802,7 @@
         <v>96.5</v>
       </c>
     </row>
-    <row r="222" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A222" s="40">
         <v>104</v>
       </c>
@@ -16845,7 +16843,7 @@
         <v>96.5</v>
       </c>
     </row>
-    <row r="223" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A223" s="40">
         <v>104</v>
       </c>
@@ -16886,7 +16884,7 @@
         <v>96.5</v>
       </c>
     </row>
-    <row r="224" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A224" s="40">
         <v>104</v>
       </c>
@@ -16927,7 +16925,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="225" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A225" s="40">
         <v>104</v>
       </c>
@@ -16968,7 +16966,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="226" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A226" s="40">
         <v>104</v>
       </c>
@@ -17009,7 +17007,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="227" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A227" s="40">
         <v>104</v>
       </c>
@@ -17050,7 +17048,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="228" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A228" s="40">
         <v>104</v>
       </c>
@@ -17091,7 +17089,7 @@
         <v>99.5</v>
       </c>
     </row>
-    <row r="229" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A229" s="40">
         <v>104</v>
       </c>
@@ -17132,7 +17130,7 @@
         <v>99.5</v>
       </c>
     </row>
-    <row r="230" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A230" s="40">
         <v>104</v>
       </c>
@@ -17173,7 +17171,7 @@
         <v>99.5</v>
       </c>
     </row>
-    <row r="231" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:18" s="40" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A231" s="40">
         <v>104</v>
       </c>
@@ -17214,385 +17212,385 @@
         <v>99.5</v>
       </c>
     </row>
-    <row r="232" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C232" s="38"/>
     </row>
-    <row r="234" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C234" s="38"/>
     </row>
-    <row r="235" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C235" s="38"/>
     </row>
-    <row r="236" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C236" s="38"/>
     </row>
-    <row r="237" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C237" s="38"/>
     </row>
-    <row r="238" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C238" s="38"/>
     </row>
-    <row r="239" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C239" s="38"/>
     </row>
-    <row r="240" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C240" s="38"/>
     </row>
-    <row r="241" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="241" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C241" s="38"/>
     </row>
-    <row r="242" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="242" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C242" s="38"/>
     </row>
-    <row r="243" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="243" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C243" s="38"/>
     </row>
-    <row r="244" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="244" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C244" s="38"/>
     </row>
-    <row r="245" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="245" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C245" s="38"/>
     </row>
-    <row r="246" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="246" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C246" s="38"/>
     </row>
-    <row r="247" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="247" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C247" s="38"/>
     </row>
-    <row r="249" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="249" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C249" s="38"/>
     </row>
-    <row r="250" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="250" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C250" s="38"/>
     </row>
-    <row r="251" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="251" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C251" s="38"/>
     </row>
-    <row r="252" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="252" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C252" s="38"/>
     </row>
-    <row r="253" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="253" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C253" s="38"/>
     </row>
-    <row r="254" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="254" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C254" s="38"/>
     </row>
-    <row r="255" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="255" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C255" s="38"/>
     </row>
-    <row r="256" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="256" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C256" s="38"/>
     </row>
-    <row r="257" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="257" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C257" s="38"/>
     </row>
-    <row r="258" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="258" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C258" s="38"/>
     </row>
-    <row r="259" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="259" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C259" s="38"/>
     </row>
-    <row r="260" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="260" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C260" s="38"/>
     </row>
-    <row r="261" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="261" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C261" s="38"/>
     </row>
-    <row r="262" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="262" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C262" s="38"/>
     </row>
-    <row r="264" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="264" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C264" s="38"/>
     </row>
-    <row r="265" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="265" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C265" s="38"/>
     </row>
-    <row r="266" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="266" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C266" s="38"/>
     </row>
-    <row r="267" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="267" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C267" s="38"/>
     </row>
-    <row r="268" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="268" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C268" s="38"/>
     </row>
-    <row r="269" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="269" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C269" s="38"/>
     </row>
-    <row r="270" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="270" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C270" s="38"/>
     </row>
-    <row r="271" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="271" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C271" s="38"/>
     </row>
-    <row r="272" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="272" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C272" s="38"/>
     </row>
-    <row r="273" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="273" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C273" s="38"/>
     </row>
-    <row r="274" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="274" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C274" s="38"/>
     </row>
-    <row r="275" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="275" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C275" s="38"/>
     </row>
-    <row r="276" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="276" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C276" s="38"/>
     </row>
-    <row r="277" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="277" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C277" s="38"/>
     </row>
-    <row r="279" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="279" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C279" s="38"/>
     </row>
-    <row r="280" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="280" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C280" s="38"/>
     </row>
-    <row r="281" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="281" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C281" s="38"/>
     </row>
-    <row r="282" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="282" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C282" s="38"/>
     </row>
-    <row r="283" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="283" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C283" s="38"/>
     </row>
-    <row r="284" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="284" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C284" s="38"/>
     </row>
-    <row r="285" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="285" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C285" s="38"/>
     </row>
-    <row r="286" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="286" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C286" s="38"/>
     </row>
-    <row r="287" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="287" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C287" s="38"/>
     </row>
-    <row r="288" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="288" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C288" s="38"/>
     </row>
-    <row r="289" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="289" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C289" s="38"/>
     </row>
-    <row r="290" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="290" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C290" s="38"/>
     </row>
-    <row r="291" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="291" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C291" s="38"/>
     </row>
-    <row r="292" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="292" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C292" s="38"/>
     </row>
-    <row r="294" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="294" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C294" s="38"/>
     </row>
-    <row r="295" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="295" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C295" s="38"/>
     </row>
-    <row r="296" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="296" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C296" s="38"/>
     </row>
-    <row r="297" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="297" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C297" s="38"/>
     </row>
-    <row r="298" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="298" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C298" s="38"/>
     </row>
-    <row r="299" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="299" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C299" s="38"/>
     </row>
-    <row r="300" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="300" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C300" s="38"/>
     </row>
-    <row r="301" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="301" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C301" s="38"/>
     </row>
-    <row r="302" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="302" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C302" s="38"/>
     </row>
-    <row r="303" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="303" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C303" s="38"/>
     </row>
-    <row r="304" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="304" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C304" s="38"/>
     </row>
-    <row r="305" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="305" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C305" s="38"/>
     </row>
-    <row r="306" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="306" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C306" s="38"/>
     </row>
-    <row r="307" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="307" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C307" s="38"/>
     </row>
-    <row r="309" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="309" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C309" s="38"/>
     </row>
-    <row r="310" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="310" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C310" s="38"/>
     </row>
-    <row r="311" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="311" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C311" s="38"/>
     </row>
-    <row r="312" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="312" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C312" s="38"/>
     </row>
-    <row r="313" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="313" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C313" s="38"/>
     </row>
-    <row r="314" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="314" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C314" s="38"/>
     </row>
-    <row r="315" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="315" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C315" s="38"/>
     </row>
-    <row r="316" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="316" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C316" s="38"/>
     </row>
-    <row r="317" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="317" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C317" s="38"/>
     </row>
-    <row r="318" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="318" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C318" s="38"/>
     </row>
-    <row r="319" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="319" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C319" s="38"/>
     </row>
-    <row r="320" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="320" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C320" s="38"/>
     </row>
-    <row r="321" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="321" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C321" s="38"/>
     </row>
-    <row r="322" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="322" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C322" s="38"/>
     </row>
-    <row r="324" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="324" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C324" s="38"/>
     </row>
-    <row r="325" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="325" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C325" s="38"/>
     </row>
-    <row r="326" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="326" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C326" s="38"/>
     </row>
-    <row r="327" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="327" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C327" s="38"/>
     </row>
-    <row r="328" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="328" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C328" s="38"/>
     </row>
-    <row r="329" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="329" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C329" s="38"/>
     </row>
-    <row r="330" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="330" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C330" s="38"/>
     </row>
-    <row r="331" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="331" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C331" s="38"/>
     </row>
-    <row r="332" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="332" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C332" s="38"/>
     </row>
-    <row r="333" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="333" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C333" s="38"/>
     </row>
-    <row r="334" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="334" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C334" s="38"/>
     </row>
-    <row r="335" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="335" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C335" s="38"/>
     </row>
-    <row r="336" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="336" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C336" s="38"/>
     </row>
-    <row r="337" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="337" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C337" s="38"/>
     </row>
-    <row r="339" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="339" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C339" s="38"/>
     </row>
-    <row r="340" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="340" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C340" s="38"/>
     </row>
-    <row r="341" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="341" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C341" s="38"/>
     </row>
-    <row r="342" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="342" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C342" s="38"/>
     </row>
-    <row r="343" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="343" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C343" s="38"/>
     </row>
-    <row r="344" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="344" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C344" s="38"/>
     </row>
-    <row r="345" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="345" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C345" s="38"/>
     </row>
-    <row r="346" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="346" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C346" s="38"/>
     </row>
-    <row r="347" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="347" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C347" s="38"/>
     </row>
-    <row r="348" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="348" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C348" s="38"/>
     </row>
-    <row r="349" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="349" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C349" s="38"/>
     </row>
-    <row r="350" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="350" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C350" s="38"/>
     </row>
-    <row r="351" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="351" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C351" s="38"/>
     </row>
-    <row r="352" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="352" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C352" s="38"/>
     </row>
-    <row r="354" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="354" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C354" s="38"/>
     </row>
-    <row r="355" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="355" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C355" s="38"/>
     </row>
-    <row r="356" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="356" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C356" s="38"/>
     </row>
-    <row r="357" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="357" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C357" s="38"/>
     </row>
-    <row r="358" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="358" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C358" s="38"/>
     </row>
-    <row r="359" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="359" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C359" s="38"/>
     </row>
-    <row r="360" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="360" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C360" s="38"/>
     </row>
-    <row r="361" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="361" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C361" s="38"/>
     </row>
-    <row r="362" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="362" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C362" s="38"/>
     </row>
-    <row r="363" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="363" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C363" s="38"/>
     </row>
-    <row r="364" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="364" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C364" s="38"/>
     </row>
-    <row r="365" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="365" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C365" s="38"/>
     </row>
-    <row r="366" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="366" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C366" s="38"/>
     </row>
-    <row r="367" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="367" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C367" s="38"/>
     </row>
   </sheetData>
@@ -17622,19 +17620,19 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:X18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="85.125" style="11" customWidth="1"/>
+    <col min="1" max="1" width="85.08203125" style="11" customWidth="1"/>
     <col min="2" max="11" width="9" style="11" customWidth="1"/>
-    <col min="12" max="12" width="9.625" style="11" customWidth="1"/>
+    <col min="12" max="12" width="9.58203125" style="11" customWidth="1"/>
     <col min="13" max="13" width="13" style="11" customWidth="1"/>
-    <col min="14" max="14" width="11.375" style="11" customWidth="1"/>
+    <col min="14" max="14" width="11.33203125" style="11" customWidth="1"/>
     <col min="15" max="15" width="9" style="11" customWidth="1"/>
     <col min="16" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -17697,7 +17695,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="3" spans="1:24" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:24" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>4</v>
       </c>
@@ -17760,7 +17758,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" s="11">
         <v>1</v>
       </c>
@@ -17841,7 +17839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
         <v>2</v>
       </c>
@@ -17922,7 +17920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
         <v>3</v>
       </c>
@@ -18003,7 +18001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
         <v>4</v>
       </c>
@@ -18084,7 +18082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
         <v>5</v>
       </c>
@@ -18165,7 +18163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
         <v>7</v>
       </c>
@@ -18246,7 +18244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
         <v>8</v>
       </c>
@@ -18327,7 +18325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" s="11">
         <v>9</v>
       </c>
@@ -18406,7 +18404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
         <v>10</v>
       </c>
@@ -18486,7 +18484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" s="11">
         <v>11</v>
       </c>
@@ -18568,7 +18566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14" s="11">
         <v>12</v>
       </c>
@@ -18650,7 +18648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15" s="11">
         <v>13</v>
       </c>
@@ -18729,7 +18727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16" s="11">
         <v>14</v>
       </c>
@@ -18810,7 +18808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17" s="11">
         <v>15</v>
       </c>
@@ -18891,7 +18889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18" s="11">
         <v>16</v>
       </c>
@@ -18982,40 +18980,40 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{800A2E94-7BD8-40B3-9D3F-70314ADBC590}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="94.625" customWidth="1"/>
+    <col min="1" max="1" width="94.58203125" customWidth="1"/>
     <col min="2" max="2" width="58.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" s="29" t="s">
         <v>746</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="58" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="55" t="s">
         <v>740</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="58" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="55" t="s">
         <v>741</v>
       </c>
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="55" t="s">
         <v>742</v>
       </c>
-      <c r="C2" s="57">
+      <c r="C2" s="54">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="58" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="55" t="s">
         <v>743</v>
       </c>
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="55" t="s">
         <v>744</v>
       </c>
-      <c r="C3" s="58" t="s">
+      <c r="C3" s="55" t="s">
         <v>745</v>
       </c>
     </row>
@@ -19028,12 +19026,12 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>649</v>
       </c>
@@ -19044,7 +19042,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>652</v>
       </c>
@@ -19055,7 +19053,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>654</v>
       </c>
@@ -19075,25 +19073,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.875" style="11" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="11" customWidth="1"/>
     <col min="2" max="3" width="16.25" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="18.375" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.375" style="11" customWidth="1"/>
+    <col min="4" max="5" width="18.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" style="11" customWidth="1"/>
     <col min="7" max="7" width="11.75" style="11" customWidth="1"/>
     <col min="8" max="8" width="18.75" style="11" customWidth="1"/>
     <col min="9" max="9" width="9" style="11" customWidth="1"/>
     <col min="10" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F1" s="7"/>
     </row>
-    <row r="2" spans="1:8" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>14</v>
       </c>
@@ -19119,7 +19117,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -19142,422 +19140,422 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="53">
+    <row r="4" spans="1:8" s="59" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="56">
         <v>1</v>
       </c>
-      <c r="B4" s="53" t="s">
+      <c r="B4" s="56" t="s">
         <v>726</v>
       </c>
-      <c r="C4" s="53" t="s">
+      <c r="C4" s="56" t="s">
         <v>726</v>
       </c>
-      <c r="D4" s="53" t="s">
+      <c r="D4" s="56" t="s">
         <v>727</v>
       </c>
-      <c r="E4" s="53" t="s">
+      <c r="E4" s="56" t="s">
         <v>727</v>
       </c>
-      <c r="F4" s="54" t="s">
+      <c r="F4" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="53">
+      <c r="G4" s="56">
         <v>202</v>
       </c>
-      <c r="H4" s="53" t="s">
+      <c r="H4" s="56" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="53">
+    <row r="5" spans="1:8" s="59" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="56">
         <v>2</v>
       </c>
-      <c r="B5" s="53" t="s">
+      <c r="B5" s="56" t="s">
         <v>703</v>
       </c>
-      <c r="C5" s="53" t="s">
+      <c r="C5" s="56" t="s">
         <v>703</v>
       </c>
-      <c r="D5" s="53" t="s">
+      <c r="D5" s="56" t="s">
         <v>704</v>
       </c>
-      <c r="E5" s="53" t="s">
+      <c r="E5" s="56" t="s">
         <v>704</v>
       </c>
-      <c r="F5" s="54" t="s">
+      <c r="F5" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="53">
+      <c r="G5" s="56">
         <v>203</v>
       </c>
-      <c r="H5" s="53" t="s">
+      <c r="H5" s="56" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="53">
+    <row r="6" spans="1:8" s="59" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="56">
         <v>3</v>
       </c>
-      <c r="B6" s="53" t="s">
+      <c r="B6" s="56" t="s">
         <v>705</v>
       </c>
-      <c r="C6" s="53" t="s">
+      <c r="C6" s="56" t="s">
         <v>705</v>
       </c>
-      <c r="D6" s="53" t="s">
+      <c r="D6" s="56" t="s">
         <v>706</v>
       </c>
-      <c r="E6" s="53" t="s">
+      <c r="E6" s="56" t="s">
         <v>706</v>
       </c>
-      <c r="F6" s="54" t="s">
+      <c r="F6" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="53">
+      <c r="G6" s="56">
         <v>204</v>
       </c>
-      <c r="H6" s="53" t="s">
+      <c r="H6" s="56" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="53">
+    <row r="7" spans="1:8" s="59" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="56">
         <v>4</v>
       </c>
-      <c r="B7" s="53" t="s">
+      <c r="B7" s="56" t="s">
         <v>707</v>
       </c>
-      <c r="C7" s="53" t="s">
+      <c r="C7" s="56" t="s">
         <v>707</v>
       </c>
-      <c r="D7" s="53" t="s">
+      <c r="D7" s="56" t="s">
         <v>708</v>
       </c>
-      <c r="E7" s="53" t="s">
+      <c r="E7" s="56" t="s">
         <v>708</v>
       </c>
-      <c r="F7" s="54" t="s">
+      <c r="F7" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="53">
+      <c r="G7" s="56">
         <v>205</v>
       </c>
-      <c r="H7" s="53" t="s">
+      <c r="H7" s="56" t="s">
         <v>709</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="53">
+    <row r="8" spans="1:8" s="59" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="56">
         <v>5</v>
       </c>
-      <c r="B8" s="53" t="s">
+      <c r="B8" s="56" t="s">
         <v>710</v>
       </c>
-      <c r="C8" s="53" t="s">
+      <c r="C8" s="56" t="s">
         <v>710</v>
       </c>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="55">
+      <c r="D8" s="56"/>
+      <c r="E8" s="56"/>
+      <c r="F8" s="58">
         <v>1</v>
       </c>
-      <c r="G8" s="53">
+      <c r="G8" s="56">
         <v>206</v>
       </c>
-      <c r="H8" s="53" t="s">
+      <c r="H8" s="56" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="53">
+    <row r="9" spans="1:8" s="59" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="56">
         <v>6</v>
       </c>
-      <c r="B9" s="53" t="s">
+      <c r="B9" s="56" t="s">
         <v>711</v>
       </c>
-      <c r="C9" s="53" t="s">
+      <c r="C9" s="56" t="s">
         <v>711</v>
       </c>
-      <c r="D9" s="53" t="s">
+      <c r="D9" s="56" t="s">
         <v>712</v>
       </c>
-      <c r="E9" s="53" t="s">
+      <c r="E9" s="56" t="s">
         <v>712</v>
       </c>
-      <c r="F9" s="54" t="s">
+      <c r="F9" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="53">
+      <c r="G9" s="56">
         <v>207</v>
       </c>
-      <c r="H9" s="53" t="s">
+      <c r="H9" s="56" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="53">
+    <row r="10" spans="1:8" s="59" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="56">
         <v>7</v>
       </c>
-      <c r="B10" s="53" t="s">
+      <c r="B10" s="56" t="s">
         <v>713</v>
       </c>
-      <c r="C10" s="53" t="s">
+      <c r="C10" s="56" t="s">
         <v>713</v>
       </c>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="55">
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
+      <c r="F10" s="58">
         <v>1</v>
       </c>
-      <c r="G10" s="53">
+      <c r="G10" s="56">
         <v>209</v>
       </c>
-      <c r="H10" s="53" t="s">
+      <c r="H10" s="56" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="53">
+    <row r="11" spans="1:8" s="59" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="56">
         <v>8</v>
       </c>
-      <c r="B11" s="53" t="s">
+      <c r="B11" s="56" t="s">
         <v>714</v>
       </c>
-      <c r="C11" s="53" t="s">
+      <c r="C11" s="56" t="s">
         <v>714</v>
       </c>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="55">
+      <c r="D11" s="56"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="58">
         <v>1</v>
       </c>
-      <c r="G11" s="53">
+      <c r="G11" s="56">
         <v>211</v>
       </c>
-      <c r="H11" s="53" t="s">
+      <c r="H11" s="56" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="53">
+    <row r="12" spans="1:8" s="59" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="56">
         <v>9</v>
       </c>
-      <c r="B12" s="53" t="s">
+      <c r="B12" s="56" t="s">
         <v>723</v>
       </c>
-      <c r="C12" s="53" t="s">
+      <c r="C12" s="56" t="s">
         <v>723</v>
       </c>
-      <c r="D12" s="53"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="55">
+      <c r="D12" s="56"/>
+      <c r="E12" s="56"/>
+      <c r="F12" s="58">
         <v>1</v>
       </c>
-      <c r="G12" s="53">
+      <c r="G12" s="56">
         <v>222</v>
       </c>
-      <c r="H12" s="53" t="s">
+      <c r="H12" s="56" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="53">
+    <row r="13" spans="1:8" s="59" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="56">
         <v>10</v>
       </c>
-      <c r="B13" s="53" t="s">
+      <c r="B13" s="56" t="s">
         <v>715</v>
       </c>
-      <c r="C13" s="53" t="s">
+      <c r="C13" s="56" t="s">
         <v>715</v>
       </c>
-      <c r="D13" s="53"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="55">
+      <c r="D13" s="56"/>
+      <c r="E13" s="56"/>
+      <c r="F13" s="58">
         <v>1</v>
       </c>
-      <c r="G13" s="53">
+      <c r="G13" s="56">
         <v>224</v>
       </c>
-      <c r="H13" s="53" t="s">
+      <c r="H13" s="56" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="53">
+    <row r="14" spans="1:8" s="59" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="56">
         <v>11</v>
       </c>
-      <c r="B14" s="53" t="s">
+      <c r="B14" s="56" t="s">
         <v>716</v>
       </c>
-      <c r="C14" s="53" t="s">
+      <c r="C14" s="56" t="s">
         <v>716</v>
       </c>
-      <c r="D14" s="53"/>
-      <c r="E14" s="53"/>
-      <c r="F14" s="55">
+      <c r="D14" s="56"/>
+      <c r="E14" s="56"/>
+      <c r="F14" s="58">
         <v>1</v>
       </c>
-      <c r="G14" s="53">
+      <c r="G14" s="56">
         <v>229</v>
       </c>
-      <c r="H14" s="53" t="s">
+      <c r="H14" s="56" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="53">
+    <row r="15" spans="1:8" s="59" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="56">
         <v>12</v>
       </c>
-      <c r="B15" s="53" t="s">
+      <c r="B15" s="56" t="s">
         <v>717</v>
       </c>
-      <c r="C15" s="53" t="s">
+      <c r="C15" s="56" t="s">
         <v>717</v>
       </c>
-      <c r="D15" s="53"/>
-      <c r="E15" s="53"/>
-      <c r="F15" s="55">
+      <c r="D15" s="56"/>
+      <c r="E15" s="56"/>
+      <c r="F15" s="58">
         <v>1</v>
       </c>
-      <c r="G15" s="53">
+      <c r="G15" s="56">
         <v>230</v>
       </c>
-      <c r="H15" s="53" t="s">
+      <c r="H15" s="56" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="53">
+    <row r="16" spans="1:8" s="59" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="56">
         <v>13</v>
       </c>
-      <c r="B16" s="53" t="s">
+      <c r="B16" s="56" t="s">
         <v>718</v>
       </c>
-      <c r="C16" s="53" t="s">
+      <c r="C16" s="56" t="s">
         <v>718</v>
       </c>
-      <c r="D16" s="53"/>
-      <c r="E16" s="53"/>
-      <c r="F16" s="55">
+      <c r="D16" s="56"/>
+      <c r="E16" s="56"/>
+      <c r="F16" s="58">
         <v>1</v>
       </c>
-      <c r="G16" s="53">
+      <c r="G16" s="56">
         <v>231</v>
       </c>
-      <c r="H16" s="53" t="s">
+      <c r="H16" s="56" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="53">
+    <row r="17" spans="1:8" s="59" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="56">
         <v>14</v>
       </c>
-      <c r="B17" s="53" t="s">
+      <c r="B17" s="56" t="s">
         <v>719</v>
       </c>
-      <c r="C17" s="53" t="s">
+      <c r="C17" s="56" t="s">
         <v>719</v>
       </c>
-      <c r="D17" s="53"/>
-      <c r="E17" s="53"/>
-      <c r="F17" s="55">
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
+      <c r="F17" s="58">
         <v>1</v>
       </c>
-      <c r="G17" s="53">
+      <c r="G17" s="56">
         <v>232</v>
       </c>
-      <c r="H17" s="53" t="s">
+      <c r="H17" s="56" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="53">
+    <row r="18" spans="1:8" s="59" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="56">
         <v>15</v>
       </c>
-      <c r="B18" s="53" t="s">
+      <c r="B18" s="56" t="s">
         <v>720</v>
       </c>
-      <c r="C18" s="53" t="s">
+      <c r="C18" s="56" t="s">
         <v>720</v>
       </c>
-      <c r="D18" s="53" t="s">
+      <c r="D18" s="56" t="s">
         <v>721</v>
       </c>
-      <c r="E18" s="53" t="s">
+      <c r="E18" s="56" t="s">
         <v>721</v>
       </c>
-      <c r="F18" s="54" t="s">
+      <c r="F18" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="G18" s="53">
+      <c r="G18" s="56">
         <v>234</v>
       </c>
-      <c r="H18" s="53" t="s">
+      <c r="H18" s="56" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="53">
+    <row r="19" spans="1:8" s="59" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="56">
         <v>16</v>
       </c>
-      <c r="B19" s="53" t="s">
+      <c r="B19" s="56" t="s">
         <v>724</v>
       </c>
-      <c r="C19" s="53" t="s">
+      <c r="C19" s="56" t="s">
         <v>724</v>
       </c>
-      <c r="D19" s="53"/>
-      <c r="E19" s="53"/>
-      <c r="F19" s="55">
+      <c r="D19" s="56"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="58">
         <v>1</v>
       </c>
-      <c r="G19" s="53">
+      <c r="G19" s="56">
         <v>237</v>
       </c>
-      <c r="H19" s="53" t="s">
+      <c r="H19" s="56" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="53">
+    <row r="20" spans="1:8" s="59" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="56">
         <v>17</v>
       </c>
-      <c r="B20" s="53" t="s">
+      <c r="B20" s="56" t="s">
         <v>725</v>
       </c>
-      <c r="C20" s="53" t="s">
+      <c r="C20" s="56" t="s">
         <v>725</v>
       </c>
-      <c r="D20" s="53"/>
-      <c r="E20" s="53"/>
-      <c r="F20" s="55">
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="58">
         <v>1</v>
       </c>
-      <c r="G20" s="53">
+      <c r="G20" s="56">
         <v>400</v>
       </c>
-      <c r="H20" s="53" t="s">
+      <c r="H20" s="56" t="s">
         <v>722</v>
       </c>
     </row>
-    <row r="21" spans="1:8" s="43" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="59">
+    <row r="21" spans="1:8" s="59" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="56">
         <v>18</v>
       </c>
-      <c r="B21" s="43" t="s">
+      <c r="B21" s="59" t="s">
+        <v>749</v>
+      </c>
+      <c r="C21" s="59" t="s">
+        <v>749</v>
+      </c>
+      <c r="F21" s="59">
+        <v>1</v>
+      </c>
+      <c r="G21" s="59">
+        <v>410</v>
+      </c>
+      <c r="H21" s="59" t="s">
         <v>748</v>
-      </c>
-      <c r="C21" s="43" t="s">
-        <v>748</v>
-      </c>
-      <c r="F21" s="43">
-        <v>1</v>
-      </c>
-      <c r="G21" s="43">
-        <v>410</v>
-      </c>
-      <c r="H21" s="43" t="s">
-        <v>749</v>
       </c>
     </row>
   </sheetData>
@@ -19570,26 +19568,26 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G173"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G171"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.25" style="11" customWidth="1"/>
     <col min="2" max="2" width="12" style="11" customWidth="1"/>
-    <col min="3" max="3" width="11.375" style="11" customWidth="1"/>
-    <col min="4" max="4" width="12.875" style="11" customWidth="1"/>
-    <col min="5" max="5" width="12.375" style="11" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" style="11" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" style="11" customWidth="1"/>
+    <col min="5" max="5" width="45.58203125" style="11" customWidth="1"/>
     <col min="6" max="6" width="13.75" style="11" customWidth="1"/>
-    <col min="7" max="7" width="15.375" style="11" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" style="11" customWidth="1"/>
     <col min="8" max="8" width="9" style="11" customWidth="1"/>
     <col min="9" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>50</v>
       </c>
@@ -19612,7 +19610,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>56</v>
       </c>
@@ -19635,7 +19633,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="11">
         <v>201</v>
       </c>
@@ -19658,35 +19656,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
       <c r="G5" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C6" s="12"/>
       <c r="D6" s="12"/>
       <c r="G6" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C7" s="12"/>
       <c r="D7" s="12"/>
       <c r="G7" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C8" s="12"/>
       <c r="D8" s="12"/>
       <c r="G8" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
         <v>202</v>
       </c>
@@ -19709,35 +19707,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
       <c r="G10" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
       <c r="G11" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C12" s="12"/>
       <c r="D12" s="12"/>
       <c r="G12" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C13" s="12"/>
       <c r="D13" s="12"/>
       <c r="G13" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="11">
         <v>203</v>
       </c>
@@ -19760,35 +19758,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C15" s="12"/>
       <c r="D15" s="12"/>
       <c r="G15" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C16" s="12"/>
       <c r="D16" s="12"/>
       <c r="G16" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
       <c r="G17" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
       <c r="G18" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="11">
         <v>204</v>
       </c>
@@ -19811,35 +19809,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
       <c r="G20" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
       <c r="G21" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
       <c r="G22" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
       <c r="G23" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="11">
         <v>205</v>
       </c>
@@ -19862,35 +19860,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
       <c r="G25" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
       <c r="G26" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
       <c r="G27" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
       <c r="G28" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="11">
         <v>206</v>
       </c>
@@ -19913,35 +19911,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
       <c r="G30" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
       <c r="G31" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
       <c r="G32" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
       <c r="G33" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="11">
         <v>207</v>
       </c>
@@ -19964,23 +19962,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C38" s="12"/>
       <c r="D38" s="12"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="11">
         <v>208</v>
       </c>
@@ -20003,35 +20001,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C40" s="12"/>
       <c r="D40" s="12"/>
       <c r="G40" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
       <c r="G41" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C42" s="12"/>
       <c r="D42" s="12"/>
       <c r="G42" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C43" s="12"/>
       <c r="D43" s="12"/>
       <c r="G43" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="11">
         <v>209</v>
       </c>
@@ -20054,35 +20052,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C45" s="12"/>
       <c r="D45" s="12"/>
       <c r="G45" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C46" s="12"/>
       <c r="D46" s="12"/>
       <c r="G46" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C47" s="12"/>
       <c r="D47" s="12"/>
       <c r="G47" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C48" s="12"/>
       <c r="D48" s="12"/>
       <c r="G48" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="11">
         <v>210</v>
       </c>
@@ -20105,35 +20103,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C50" s="12"/>
       <c r="D50" s="12"/>
       <c r="G50" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C51" s="12"/>
       <c r="D51" s="12"/>
       <c r="G51" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C52" s="12"/>
       <c r="D52" s="12"/>
       <c r="G52" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C53" s="12"/>
       <c r="D53" s="12"/>
       <c r="G53" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="11">
         <v>211</v>
       </c>
@@ -20156,35 +20154,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C55" s="12"/>
       <c r="D55" s="12"/>
       <c r="G55" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C56" s="12"/>
       <c r="D56" s="12"/>
       <c r="G56" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C57" s="12"/>
       <c r="D57" s="12"/>
       <c r="G57" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C58" s="12"/>
       <c r="D58" s="12"/>
       <c r="G58" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="11">
         <v>212</v>
       </c>
@@ -20203,35 +20201,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C60" s="12"/>
       <c r="D60" s="12"/>
       <c r="G60" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C61" s="12"/>
       <c r="D61" s="12"/>
       <c r="G61" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C62" s="12"/>
       <c r="D62" s="12"/>
       <c r="G62" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C63" s="12"/>
       <c r="D63" s="12"/>
       <c r="G63" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="11">
         <v>213</v>
       </c>
@@ -20250,35 +20248,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C65" s="12"/>
       <c r="D65" s="12"/>
       <c r="G65" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C66" s="12"/>
       <c r="D66" s="12"/>
       <c r="G66" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C67" s="12"/>
       <c r="D67" s="12"/>
       <c r="G67" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C68" s="12"/>
       <c r="D68" s="12"/>
       <c r="G68" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="11">
         <v>214</v>
       </c>
@@ -20297,35 +20295,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C70" s="12"/>
       <c r="D70" s="12"/>
       <c r="G70" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C71" s="12"/>
       <c r="D71" s="12"/>
       <c r="G71" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C72" s="12"/>
       <c r="D72" s="12"/>
       <c r="G72" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C73" s="12"/>
       <c r="D73" s="12"/>
       <c r="G73" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="11">
         <v>215</v>
       </c>
@@ -20344,35 +20342,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C75" s="12"/>
       <c r="D75" s="12"/>
       <c r="G75" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C76" s="12"/>
       <c r="D76" s="12"/>
       <c r="G76" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C77" s="12"/>
       <c r="D77" s="12"/>
       <c r="G77" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C78" s="12"/>
       <c r="D78" s="12"/>
       <c r="G78" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="11">
         <v>216</v>
       </c>
@@ -20391,35 +20389,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C80" s="12"/>
       <c r="D80" s="12"/>
       <c r="G80" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C81" s="12"/>
       <c r="D81" s="12"/>
       <c r="G81" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C82" s="12"/>
       <c r="D82" s="12"/>
       <c r="G82" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C83" s="12"/>
       <c r="D83" s="12"/>
       <c r="G83" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="11">
         <v>222</v>
       </c>
@@ -20442,35 +20440,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C85" s="12"/>
       <c r="D85" s="12"/>
       <c r="G85" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C86" s="12"/>
       <c r="D86" s="12"/>
       <c r="G86" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C87" s="12"/>
       <c r="D87" s="12"/>
       <c r="G87" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C88" s="12"/>
       <c r="D88" s="12"/>
       <c r="G88" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="11">
         <v>223</v>
       </c>
@@ -20493,35 +20491,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C90" s="12"/>
       <c r="D90" s="12"/>
       <c r="G90" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C91" s="12"/>
       <c r="D91" s="12"/>
       <c r="G91" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C92" s="12"/>
       <c r="D92" s="12"/>
       <c r="G92" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C93" s="12"/>
       <c r="D93" s="12"/>
       <c r="G93" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="11">
         <v>224</v>
       </c>
@@ -20544,35 +20542,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C95" s="12"/>
       <c r="D95" s="12"/>
       <c r="G95" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C96" s="12"/>
       <c r="D96" s="12"/>
       <c r="G96" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C97" s="12"/>
       <c r="D97" s="12"/>
       <c r="G97" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C98" s="12"/>
       <c r="D98" s="12"/>
       <c r="G98" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="11">
         <v>225</v>
       </c>
@@ -20595,35 +20593,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C100" s="12"/>
       <c r="D100" s="12"/>
       <c r="G100" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C101" s="12"/>
       <c r="D101" s="12"/>
       <c r="G101" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C102" s="12"/>
       <c r="D102" s="12"/>
       <c r="G102" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C103" s="12"/>
       <c r="D103" s="12"/>
       <c r="G103" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="11">
         <v>226</v>
       </c>
@@ -20646,35 +20644,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C105" s="12"/>
       <c r="D105" s="12"/>
       <c r="G105" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C106" s="12"/>
       <c r="D106" s="12"/>
       <c r="G106" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C107" s="12"/>
       <c r="D107" s="12"/>
       <c r="G107" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C108" s="12"/>
       <c r="D108" s="12"/>
       <c r="G108" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="11">
         <v>227</v>
       </c>
@@ -20697,35 +20695,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C110" s="12"/>
       <c r="D110" s="12"/>
       <c r="G110" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C111" s="12"/>
       <c r="D111" s="12"/>
       <c r="G111" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C112" s="12"/>
       <c r="D112" s="12"/>
       <c r="G112" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C113" s="12"/>
       <c r="D113" s="12"/>
       <c r="G113" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="11">
         <v>228</v>
       </c>
@@ -20748,35 +20746,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C115" s="12"/>
       <c r="D115" s="12"/>
       <c r="G115" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C116" s="12"/>
       <c r="D116" s="12"/>
       <c r="G116" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C117" s="12"/>
       <c r="D117" s="12"/>
       <c r="G117" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C118" s="12"/>
       <c r="D118" s="12"/>
       <c r="G118" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="11">
         <v>229</v>
       </c>
@@ -20799,35 +20797,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C120" s="12"/>
       <c r="D120" s="12"/>
       <c r="G120" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C121" s="12"/>
       <c r="D121" s="12"/>
       <c r="G121" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C122" s="12"/>
       <c r="D122" s="12"/>
       <c r="G122" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C123" s="12"/>
       <c r="D123" s="12"/>
       <c r="G123" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" s="11">
         <v>230</v>
       </c>
@@ -20850,35 +20848,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C125" s="12"/>
       <c r="D125" s="12"/>
       <c r="G125" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C126" s="12"/>
       <c r="D126" s="12"/>
       <c r="G126" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C127" s="12"/>
       <c r="D127" s="12"/>
       <c r="G127" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C128" s="12"/>
       <c r="D128" s="12"/>
       <c r="G128" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" s="11">
         <v>231</v>
       </c>
@@ -20901,35 +20899,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C130" s="12"/>
       <c r="D130" s="12"/>
       <c r="G130" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C131" s="12"/>
       <c r="D131" s="12"/>
       <c r="G131" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C132" s="12"/>
       <c r="D132" s="12"/>
       <c r="G132" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C133" s="12"/>
       <c r="D133" s="12"/>
       <c r="G133" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" s="11">
         <v>232</v>
       </c>
@@ -20952,35 +20950,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C135" s="12"/>
       <c r="D135" s="12"/>
       <c r="G135" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C136" s="12"/>
       <c r="D136" s="12"/>
       <c r="G136" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C137" s="12"/>
       <c r="D137" s="12"/>
       <c r="G137" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C138" s="12"/>
       <c r="D138" s="12"/>
       <c r="G138" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" s="11">
         <v>233</v>
       </c>
@@ -21003,35 +21001,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C140" s="12"/>
       <c r="D140" s="12"/>
       <c r="G140" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C141" s="12"/>
       <c r="D141" s="12"/>
       <c r="G141" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C142" s="12"/>
       <c r="D142" s="12"/>
       <c r="G142" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C143" s="12"/>
       <c r="D143" s="12"/>
       <c r="G143" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" s="11">
         <v>234</v>
       </c>
@@ -21054,35 +21052,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C145" s="12"/>
       <c r="D145" s="12"/>
       <c r="G145" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C146" s="12"/>
       <c r="D146" s="12"/>
       <c r="G146" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C147" s="12"/>
       <c r="D147" s="12"/>
       <c r="G147" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C148" s="12"/>
       <c r="D148" s="12"/>
       <c r="G148" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" s="11">
         <v>235</v>
       </c>
@@ -21105,35 +21103,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C150" s="12"/>
       <c r="D150" s="12"/>
       <c r="G150" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C151" s="12"/>
       <c r="D151" s="12"/>
       <c r="G151" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C152" s="12"/>
       <c r="D152" s="12"/>
       <c r="G152" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C153" s="12"/>
       <c r="D153" s="12"/>
       <c r="G153" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:7" ht="26.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="11">
         <v>236</v>
       </c>
@@ -21150,17 +21148,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G155" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G156" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" s="11">
         <v>237</v>
       </c>
@@ -21173,8 +21171,8 @@
       <c r="D157" s="12">
         <v>10</v>
       </c>
-      <c r="E157" s="11" t="s">
-        <v>64</v>
+      <c r="E157" s="43" t="s">
+        <v>750</v>
       </c>
       <c r="F157" s="11">
         <v>237</v>
@@ -21183,35 +21181,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C158" s="12"/>
       <c r="D158" s="12"/>
       <c r="G158" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C159" s="12"/>
       <c r="D159" s="12"/>
       <c r="G159" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C160" s="12"/>
       <c r="D160" s="12"/>
       <c r="G160" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C161" s="12"/>
       <c r="D161" s="12"/>
       <c r="G161" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A162" s="43">
         <v>300</v>
       </c>
@@ -21234,27 +21232,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.3">
       <c r="G163" s="43">
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.3">
       <c r="G164" s="43">
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.3">
       <c r="G165" s="43">
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.3">
       <c r="G166" s="43">
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" s="11">
         <v>400</v>
       </c>
@@ -21277,51 +21275,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G168" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G169" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A170" s="11">
+        <v>410</v>
+      </c>
+      <c r="B170" s="43" t="s">
+        <v>747</v>
+      </c>
+      <c r="C170" s="11">
+        <v>3</v>
+      </c>
+      <c r="D170" s="11">
+        <v>4</v>
+      </c>
+      <c r="E170" s="43" t="s">
+        <v>750</v>
+      </c>
+      <c r="F170" s="11">
+        <v>410</v>
+      </c>
       <c r="G170" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G171" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A172" s="43">
-        <v>410</v>
-      </c>
-      <c r="B172" s="43" t="s">
-        <v>747</v>
-      </c>
-      <c r="C172" s="43">
-        <v>3</v>
-      </c>
-      <c r="D172" s="43">
-        <v>4</v>
-      </c>
-      <c r="E172" s="43" t="s">
-        <v>656</v>
-      </c>
-      <c r="F172" s="43">
-        <v>410</v>
-      </c>
-      <c r="G172" s="43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7" s="43" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="G173" s="43">
         <v>0</v>
       </c>
     </row>
@@ -21365,20 +21353,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.25" style="11" customWidth="1"/>
-    <col min="2" max="2" width="15.875" style="11" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" style="11" customWidth="1"/>
     <col min="3" max="3" width="9" style="11" customWidth="1"/>
     <col min="4" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>83</v>
       </c>
@@ -21386,7 +21374,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>85</v>
       </c>
@@ -21394,7 +21382,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="11">
         <v>1</v>
       </c>
@@ -21402,7 +21390,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
         <v>2</v>
       </c>
@@ -21410,7 +21398,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
         <v>3</v>
       </c>
@@ -21418,7 +21406,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
         <v>4</v>
       </c>
@@ -21426,7 +21414,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
         <v>5</v>
       </c>
@@ -21444,28 +21432,28 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:M23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.25" style="11" customWidth="1"/>
     <col min="2" max="2" width="23.25" style="11" customWidth="1"/>
     <col min="3" max="3" width="14.25" style="11" customWidth="1"/>
-    <col min="4" max="8" width="9.125" style="11" customWidth="1"/>
+    <col min="4" max="8" width="9.08203125" style="11" customWidth="1"/>
     <col min="9" max="9" width="9" style="11" customWidth="1"/>
-    <col min="10" max="10" width="12.375" style="11" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" style="11" customWidth="1"/>
     <col min="11" max="14" width="9" style="11" customWidth="1"/>
-    <col min="15" max="15" width="9.125" style="11" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.375" style="11" bestFit="1" customWidth="1"/>
-    <col min="17" max="22" width="9.125" style="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.08203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="17" max="22" width="9.08203125" style="11" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="9" style="11" customWidth="1"/>
     <col min="24" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>736</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>738</v>
       </c>
@@ -21491,7 +21479,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>735</v>
       </c>
@@ -21517,7 +21505,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="43" t="s">
         <v>739</v>
       </c>
@@ -21553,7 +21541,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B5" s="11">
         <v>2</v>
       </c>
@@ -21586,7 +21574,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B6" s="11">
         <v>3</v>
       </c>
@@ -21621,7 +21609,7 @@
       <c r="L6" s="13"/>
       <c r="M6" s="13"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B7" s="11">
         <v>4</v>
       </c>
@@ -21654,7 +21642,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B8" s="11">
         <v>5</v>
       </c>
@@ -21687,7 +21675,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B9" s="11">
         <v>6</v>
       </c>
@@ -21697,16 +21685,16 @@
       <c r="D9" s="19">
         <v>212</v>
       </c>
-      <c r="E9" s="56">
+      <c r="E9" s="53">
         <v>108</v>
       </c>
-      <c r="F9" s="56">
+      <c r="F9" s="53">
         <v>-10</v>
       </c>
-      <c r="G9" s="56">
+      <c r="G9" s="53">
         <v>69</v>
       </c>
-      <c r="H9" s="56">
+      <c r="H9" s="53">
         <v>2</v>
       </c>
       <c r="I9" s="19" t="str">
@@ -21720,7 +21708,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B10" s="11">
         <v>7</v>
       </c>
@@ -21730,16 +21718,16 @@
       <c r="D10" s="44">
         <v>236</v>
       </c>
-      <c r="E10" s="56">
+      <c r="E10" s="53">
         <v>-42</v>
       </c>
-      <c r="F10" s="56">
+      <c r="F10" s="53">
         <v>5</v>
       </c>
-      <c r="G10" s="56">
+      <c r="G10" s="53">
         <v>5</v>
       </c>
-      <c r="H10" s="56">
+      <c r="H10" s="53">
         <v>2</v>
       </c>
       <c r="I10" s="19" t="str">
@@ -21755,7 +21743,7 @@
       <c r="L10" s="13"/>
       <c r="M10" s="13"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B11" s="11">
         <v>8</v>
       </c>
@@ -21765,16 +21753,16 @@
       <c r="D11" s="19">
         <v>208</v>
       </c>
-      <c r="E11" s="56">
+      <c r="E11" s="53">
         <v>99</v>
       </c>
-      <c r="F11" s="56">
-        <v>0</v>
-      </c>
-      <c r="G11" s="56">
-        <v>0</v>
-      </c>
-      <c r="H11" s="56">
+      <c r="F11" s="53">
+        <v>0</v>
+      </c>
+      <c r="G11" s="53">
+        <v>0</v>
+      </c>
+      <c r="H11" s="53">
         <v>2</v>
       </c>
       <c r="I11" s="19" t="str">
@@ -21788,7 +21776,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B12" s="11">
         <v>9</v>
       </c>
@@ -21798,16 +21786,16 @@
       <c r="D12" s="44">
         <v>227</v>
       </c>
-      <c r="E12" s="56">
+      <c r="E12" s="53">
         <v>164</v>
       </c>
-      <c r="F12" s="56">
-        <v>-9</v>
-      </c>
-      <c r="G12" s="56">
+      <c r="F12" s="53">
+        <v>-9</v>
+      </c>
+      <c r="G12" s="53">
         <v>12</v>
       </c>
-      <c r="H12" s="56">
+      <c r="H12" s="53">
         <v>2</v>
       </c>
       <c r="I12" s="19" t="str">
@@ -21821,7 +21809,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B13" s="11">
         <v>10</v>
       </c>
@@ -21831,16 +21819,16 @@
       <c r="D13" s="44">
         <v>227</v>
       </c>
-      <c r="E13" s="56">
+      <c r="E13" s="53">
         <v>181</v>
       </c>
-      <c r="F13" s="56">
-        <v>-9</v>
-      </c>
-      <c r="G13" s="56">
+      <c r="F13" s="53">
+        <v>-9</v>
+      </c>
+      <c r="G13" s="53">
         <v>-28</v>
       </c>
-      <c r="H13" s="56">
+      <c r="H13" s="53">
         <v>2</v>
       </c>
       <c r="I13" s="19" t="str">
@@ -21854,7 +21842,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="14" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B14" s="11">
         <v>11</v>
       </c>
@@ -21864,16 +21852,16 @@
       <c r="D14" s="45">
         <v>215</v>
       </c>
-      <c r="E14" s="56">
+      <c r="E14" s="53">
         <v>99</v>
       </c>
-      <c r="F14" s="56">
-        <v>0</v>
-      </c>
-      <c r="G14" s="56">
-        <v>0</v>
-      </c>
-      <c r="H14" s="56">
+      <c r="F14" s="53">
+        <v>0</v>
+      </c>
+      <c r="G14" s="53">
+        <v>0</v>
+      </c>
+      <c r="H14" s="53">
         <v>2</v>
       </c>
       <c r="I14" s="5" t="str">
@@ -21885,7 +21873,7 @@
       </c>
       <c r="K14" s="46"/>
     </row>
-    <row r="15" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B15" s="11">
         <v>12</v>
       </c>
@@ -21895,16 +21883,16 @@
       <c r="D15" s="45">
         <v>226</v>
       </c>
-      <c r="E15" s="56">
+      <c r="E15" s="53">
         <v>-28</v>
       </c>
-      <c r="F15" s="56">
+      <c r="F15" s="53">
         <v>3</v>
       </c>
-      <c r="G15" s="56">
+      <c r="G15" s="53">
         <v>69</v>
       </c>
-      <c r="H15" s="56">
+      <c r="H15" s="53">
         <v>2</v>
       </c>
       <c r="I15" s="5" t="str">
@@ -21916,7 +21904,7 @@
       </c>
       <c r="K15" s="46"/>
     </row>
-    <row r="16" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B16" s="11">
         <v>13</v>
       </c>
@@ -21926,16 +21914,16 @@
       <c r="D16" s="45">
         <v>206</v>
       </c>
-      <c r="E16" s="56">
+      <c r="E16" s="53">
         <v>66</v>
       </c>
-      <c r="F16" s="56">
-        <v>0</v>
-      </c>
-      <c r="G16" s="56">
+      <c r="F16" s="53">
+        <v>0</v>
+      </c>
+      <c r="G16" s="53">
         <v>42</v>
       </c>
-      <c r="H16" s="56">
+      <c r="H16" s="53">
         <v>2</v>
       </c>
       <c r="I16" s="5" t="str">
@@ -21947,7 +21935,7 @@
       </c>
       <c r="K16" s="46"/>
     </row>
-    <row r="17" spans="2:11" s="43" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:11" s="43" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B17" s="11">
         <v>15</v>
       </c>
@@ -21957,16 +21945,16 @@
       <c r="D17" s="46">
         <v>300</v>
       </c>
-      <c r="E17" s="56">
+      <c r="E17" s="53">
         <v>130</v>
       </c>
-      <c r="F17" s="56">
-        <v>-9</v>
-      </c>
-      <c r="G17" s="56">
+      <c r="F17" s="53">
+        <v>-9</v>
+      </c>
+      <c r="G17" s="53">
         <v>66</v>
       </c>
-      <c r="H17" s="56">
+      <c r="H17" s="53">
         <v>2</v>
       </c>
       <c r="I17" s="46" t="str">
@@ -21977,7 +21965,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="11">
         <v>16</v>
       </c>
@@ -21987,16 +21975,16 @@
       <c r="D18" s="13">
         <v>208</v>
       </c>
-      <c r="E18" s="56">
+      <c r="E18" s="53">
         <v>-72</v>
       </c>
-      <c r="F18" s="56">
+      <c r="F18" s="53">
         <v>13</v>
       </c>
-      <c r="G18" s="56">
+      <c r="G18" s="53">
         <v>78</v>
       </c>
-      <c r="H18" s="56">
+      <c r="H18" s="53">
         <v>3</v>
       </c>
       <c r="I18" s="11" t="str">
@@ -22008,7 +21996,7 @@
       </c>
       <c r="K18" s="43"/>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="11">
         <v>17</v>
       </c>
@@ -22018,16 +22006,16 @@
       <c r="D19" s="15">
         <v>212</v>
       </c>
-      <c r="E19" s="56">
+      <c r="E19" s="53">
         <v>108</v>
       </c>
-      <c r="F19" s="56">
+      <c r="F19" s="53">
         <v>-10</v>
       </c>
-      <c r="G19" s="56">
+      <c r="G19" s="53">
         <v>69</v>
       </c>
-      <c r="H19" s="56">
+      <c r="H19" s="53">
         <v>3</v>
       </c>
       <c r="I19" s="14" t="str">
@@ -22039,7 +22027,7 @@
       </c>
       <c r="K19" s="43"/>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="11">
         <v>18</v>
       </c>
@@ -22049,16 +22037,16 @@
       <c r="D20" s="13">
         <v>208</v>
       </c>
-      <c r="E20" s="56">
+      <c r="E20" s="53">
         <v>-72</v>
       </c>
-      <c r="F20" s="56">
+      <c r="F20" s="53">
         <v>13</v>
       </c>
-      <c r="G20" s="56">
+      <c r="G20" s="53">
         <v>78</v>
       </c>
-      <c r="H20" s="56">
+      <c r="H20" s="53">
         <v>4</v>
       </c>
       <c r="I20" s="11" t="str">
@@ -22070,7 +22058,7 @@
       </c>
       <c r="K20" s="43"/>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B21" s="11">
         <v>19</v>
       </c>
@@ -22080,16 +22068,16 @@
       <c r="D21" s="15">
         <v>212</v>
       </c>
-      <c r="E21" s="56">
+      <c r="E21" s="53">
         <v>108</v>
       </c>
-      <c r="F21" s="56">
+      <c r="F21" s="53">
         <v>-10</v>
       </c>
-      <c r="G21" s="56">
+      <c r="G21" s="53">
         <v>69</v>
       </c>
-      <c r="H21" s="56">
+      <c r="H21" s="53">
         <v>4</v>
       </c>
       <c r="I21" s="14" t="str">
@@ -22101,7 +22089,7 @@
       </c>
       <c r="K21" s="43"/>
     </row>
-    <row r="22" spans="2:11" s="43" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:11" s="43" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B22" s="43">
         <v>20</v>
       </c>
@@ -22111,16 +22099,16 @@
       <c r="D22" s="43">
         <v>213</v>
       </c>
-      <c r="E22" s="56">
+      <c r="E22" s="53">
         <v>16.5</v>
       </c>
-      <c r="F22" s="56">
+      <c r="F22" s="53">
         <v>-18.5</v>
       </c>
-      <c r="G22" s="56">
+      <c r="G22" s="53">
         <v>130.5</v>
       </c>
-      <c r="H22" s="56">
+      <c r="H22" s="53">
         <v>2</v>
       </c>
       <c r="I22" s="43" t="s">
@@ -22130,7 +22118,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B23" s="11">
         <v>21</v>
       </c>
@@ -22167,7 +22155,7 @@
   </autoFilter>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="M22">
-    <cfRule type="duplicateValues" dxfId="80" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
@@ -22177,25 +22165,25 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:H35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.75" style="11" customWidth="1"/>
-    <col min="2" max="2" width="10.125" style="11" customWidth="1"/>
-    <col min="3" max="3" width="6.625" style="11" customWidth="1"/>
-    <col min="4" max="4" width="14.625" style="11" customWidth="1"/>
-    <col min="5" max="5" width="13.375" style="11" customWidth="1"/>
+    <col min="2" max="2" width="10.08203125" style="11" customWidth="1"/>
+    <col min="3" max="3" width="6.58203125" style="11" customWidth="1"/>
+    <col min="4" max="4" width="14.58203125" style="11" customWidth="1"/>
+    <col min="5" max="5" width="13.33203125" style="11" customWidth="1"/>
     <col min="6" max="6" width="8" style="11" customWidth="1"/>
     <col min="7" max="7" width="16.75" style="11" customWidth="1"/>
     <col min="8" max="8" width="9" style="11" customWidth="1"/>
     <col min="9" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>98</v>
       </c>
@@ -22218,7 +22206,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>104</v>
       </c>
@@ -22238,7 +22226,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="11">
         <v>199</v>
       </c>
@@ -22258,7 +22246,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
         <v>199</v>
       </c>
@@ -22278,7 +22266,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
         <v>199</v>
       </c>
@@ -22298,7 +22286,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
         <v>199</v>
       </c>
@@ -22318,7 +22306,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
         <v>200</v>
       </c>
@@ -22335,7 +22323,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
         <v>200</v>
       </c>
@@ -22352,7 +22340,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
         <v>200</v>
       </c>
@@ -22369,7 +22357,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="11">
         <v>200</v>
       </c>
@@ -22386,7 +22374,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
         <v>200</v>
       </c>
@@ -22403,7 +22391,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="11">
         <v>200</v>
       </c>
@@ -22420,7 +22408,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="11">
         <v>200</v>
       </c>
@@ -22441,7 +22429,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="11">
         <v>200</v>
       </c>
@@ -22458,7 +22446,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="11">
         <v>200</v>
       </c>
@@ -22475,7 +22463,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="11">
         <v>299</v>
       </c>
@@ -22496,7 +22484,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="11">
         <v>299</v>
       </c>
@@ -22513,7 +22501,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="11">
         <v>299</v>
       </c>
@@ -22534,7 +22522,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="11">
         <v>299</v>
       </c>
@@ -22555,7 +22543,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="11">
         <v>400</v>
       </c>
@@ -22572,7 +22560,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="11">
         <v>400</v>
       </c>
@@ -22589,7 +22577,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="11">
         <v>400</v>
       </c>
@@ -22606,7 +22594,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="11">
         <v>400</v>
       </c>
@@ -22623,7 +22611,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="11">
         <v>600</v>
       </c>
@@ -22640,7 +22628,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A26" s="43">
         <v>199</v>
       </c>
@@ -22659,7 +22647,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A27" s="43">
         <v>199</v>
       </c>
@@ -22678,7 +22666,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A28" s="43">
         <v>199</v>
       </c>
@@ -22697,7 +22685,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A29" s="43">
         <v>199</v>
       </c>
@@ -22716,7 +22704,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A30" s="43">
         <v>199</v>
       </c>
@@ -22735,7 +22723,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A31" s="43">
         <v>199</v>
       </c>
@@ -22754,7 +22742,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A32" s="43">
         <v>199</v>
       </c>
@@ -22773,7 +22761,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" s="43">
         <v>199</v>
       </c>
@@ -22792,7 +22780,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" s="43">
         <v>199</v>
       </c>
@@ -22811,7 +22799,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" s="43">
         <v>199</v>
       </c>
@@ -22832,117 +22820,117 @@
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
+  <conditionalFormatting sqref="A4 A8:A20">
+    <cfRule type="duplicateValues" dxfId="79" priority="82"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A5">
+    <cfRule type="duplicateValues" dxfId="78" priority="77"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A6">
+    <cfRule type="duplicateValues" dxfId="77" priority="67"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A7">
+    <cfRule type="duplicateValues" dxfId="76" priority="72"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A21">
+    <cfRule type="duplicateValues" dxfId="75" priority="63"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A22">
+    <cfRule type="duplicateValues" dxfId="74" priority="61"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A23">
+    <cfRule type="duplicateValues" dxfId="73" priority="58"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A24">
+    <cfRule type="duplicateValues" dxfId="72" priority="55"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E1">
-    <cfRule type="duplicateValues" dxfId="79" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="149"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E3">
+    <cfRule type="duplicateValues" dxfId="70" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4">
-    <cfRule type="duplicateValues" dxfId="78" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5">
+    <cfRule type="duplicateValues" dxfId="67" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6">
+    <cfRule type="duplicateValues" dxfId="65" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E7">
+    <cfRule type="duplicateValues" dxfId="63" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8:E13">
+    <cfRule type="duplicateValues" dxfId="61" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E14:E20">
+    <cfRule type="duplicateValues" dxfId="59" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E21 E23">
+    <cfRule type="duplicateValues" dxfId="58" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E22 E24">
+    <cfRule type="duplicateValues" dxfId="57" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E25">
+    <cfRule type="duplicateValues" dxfId="56" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E26">
+    <cfRule type="duplicateValues" dxfId="54" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E27:E30">
+    <cfRule type="duplicateValues" dxfId="52" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E31:E34">
+    <cfRule type="duplicateValues" dxfId="50" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E35">
+    <cfRule type="duplicateValues" dxfId="48" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E14:F16 F17:F20">
+    <cfRule type="duplicateValues" dxfId="46" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4 F8:F13">
+    <cfRule type="duplicateValues" dxfId="45" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4">
-    <cfRule type="duplicateValues" dxfId="76" priority="42"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A5">
-    <cfRule type="duplicateValues" dxfId="75" priority="77"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="duplicateValues" dxfId="74" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5">
-    <cfRule type="duplicateValues" dxfId="72" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="40"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A6">
-    <cfRule type="duplicateValues" dxfId="70" priority="67"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="69" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6">
-    <cfRule type="duplicateValues" dxfId="67" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="36"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A7">
-    <cfRule type="duplicateValues" dxfId="65" priority="72"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="64" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="duplicateValues" dxfId="62" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="38"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A21">
-    <cfRule type="duplicateValues" dxfId="60" priority="63"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E21 E23">
-    <cfRule type="duplicateValues" dxfId="59" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F21">
-    <cfRule type="duplicateValues" dxfId="58" priority="34"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A22">
-    <cfRule type="duplicateValues" dxfId="57" priority="61"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E22 E24">
-    <cfRule type="duplicateValues" dxfId="56" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F22">
-    <cfRule type="duplicateValues" dxfId="55" priority="33"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A23">
-    <cfRule type="duplicateValues" dxfId="54" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F23">
-    <cfRule type="duplicateValues" dxfId="53" priority="31"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A24">
-    <cfRule type="duplicateValues" dxfId="52" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F24">
-    <cfRule type="duplicateValues" dxfId="51" priority="29"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E25">
-    <cfRule type="duplicateValues" dxfId="50" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E3">
-    <cfRule type="duplicateValues" dxfId="48" priority="86"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8:E13">
-    <cfRule type="duplicateValues" dxfId="47" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E14:E20">
-    <cfRule type="duplicateValues" dxfId="45" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A4 A8:A20">
-    <cfRule type="duplicateValues" dxfId="44" priority="82"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4 F8:F13">
-    <cfRule type="duplicateValues" dxfId="43" priority="41"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E14:F16 F17:F20">
-    <cfRule type="duplicateValues" dxfId="42" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E26">
-    <cfRule type="duplicateValues" dxfId="41" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E27:E30">
-    <cfRule type="duplicateValues" dxfId="39" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E31:E34">
-    <cfRule type="duplicateValues" dxfId="37" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E35">
-    <cfRule type="duplicateValues" dxfId="35" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="29"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
@@ -22952,26 +22940,26 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:X18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.75" style="11" customWidth="1"/>
     <col min="2" max="7" width="9" style="11" customWidth="1"/>
     <col min="8" max="8" width="4.25" style="11" customWidth="1"/>
     <col min="9" max="10" width="9" style="11" customWidth="1"/>
     <col min="11" max="11" width="7.75" style="11" customWidth="1"/>
-    <col min="12" max="12" width="9.625" style="11" customWidth="1"/>
+    <col min="12" max="12" width="9.58203125" style="11" customWidth="1"/>
     <col min="13" max="13" width="13" style="11" customWidth="1"/>
-    <col min="14" max="14" width="12.875" style="11" customWidth="1"/>
+    <col min="14" max="14" width="12.83203125" style="11" customWidth="1"/>
     <col min="15" max="15" width="9" style="11" customWidth="1"/>
     <col min="16" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -23034,7 +23022,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="3" spans="1:24" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:24" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>4</v>
       </c>
@@ -23097,7 +23085,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" s="11">
         <v>1</v>
       </c>
@@ -23171,7 +23159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
         <v>2</v>
       </c>
@@ -23245,7 +23233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
         <v>3</v>
       </c>
@@ -23319,7 +23307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
         <v>4</v>
       </c>
@@ -23393,7 +23381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
         <v>5</v>
       </c>
@@ -23467,7 +23455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
         <v>7</v>
       </c>
@@ -23541,7 +23529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
         <v>8</v>
       </c>
@@ -23615,7 +23603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" s="11">
         <v>9</v>
       </c>
@@ -23687,7 +23675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
         <v>10</v>
       </c>
@@ -23759,7 +23747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" s="11">
         <v>11</v>
       </c>
@@ -23833,7 +23821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14" s="11">
         <v>12</v>
       </c>
@@ -23907,7 +23895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15" s="11">
         <v>13</v>
       </c>
@@ -23979,7 +23967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16" s="11">
         <v>14</v>
       </c>
@@ -24053,7 +24041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17" s="11">
         <v>15</v>
       </c>
@@ -24127,7 +24115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18" s="11">
         <v>16</v>
       </c>
@@ -24211,30 +24199,30 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:N86"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.375" style="21" customWidth="1"/>
-    <col min="2" max="2" width="12.875" style="11" customWidth="1"/>
+    <col min="1" max="1" width="12.33203125" style="21" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" style="11" customWidth="1"/>
     <col min="3" max="3" width="7.75" style="11" customWidth="1"/>
     <col min="4" max="5" width="12.75" style="11" customWidth="1"/>
-    <col min="6" max="7" width="19.375" style="11" customWidth="1"/>
-    <col min="8" max="8" width="29.375" style="11" customWidth="1"/>
-    <col min="9" max="9" width="46.375" style="11" customWidth="1"/>
+    <col min="6" max="7" width="19.33203125" style="11" customWidth="1"/>
+    <col min="8" max="8" width="29.33203125" style="11" customWidth="1"/>
+    <col min="9" max="9" width="46.33203125" style="11" customWidth="1"/>
     <col min="10" max="10" width="23" style="11" customWidth="1"/>
-    <col min="11" max="11" width="22.375" style="11" customWidth="1"/>
-    <col min="12" max="12" width="29.125" style="11" customWidth="1"/>
-    <col min="13" max="13" width="34.375" style="11" customWidth="1"/>
-    <col min="14" max="14" width="14.375" style="11" customWidth="1"/>
+    <col min="11" max="11" width="22.33203125" style="11" customWidth="1"/>
+    <col min="12" max="12" width="29.08203125" style="11" customWidth="1"/>
+    <col min="13" max="13" width="34.33203125" style="11" customWidth="1"/>
+    <col min="14" max="14" width="14.33203125" style="11" customWidth="1"/>
     <col min="15" max="15" width="9" style="11" customWidth="1"/>
     <col min="16" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="27" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>220</v>
       </c>
@@ -24278,7 +24266,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
         <v>233</v>
       </c>
@@ -24322,7 +24310,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="21">
         <v>101001001</v>
       </c>
@@ -24366,7 +24354,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="21">
         <v>101001002</v>
       </c>
@@ -24410,7 +24398,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="21">
         <v>101001003</v>
       </c>
@@ -24454,7 +24442,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="23">
         <v>101001004</v>
       </c>
@@ -24498,7 +24486,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="23">
         <v>101001005</v>
       </c>
@@ -24542,7 +24530,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="23">
         <v>101001006</v>
       </c>
@@ -24586,7 +24574,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="23">
         <v>101001007</v>
       </c>
@@ -24630,7 +24618,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="21">
         <v>102001001</v>
       </c>
@@ -24674,7 +24662,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="21">
         <v>102001002</v>
       </c>
@@ -24718,7 +24706,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="21">
         <v>102001003</v>
       </c>
@@ -24762,7 +24750,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="23">
         <v>102001004</v>
       </c>
@@ -24806,7 +24794,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="23">
         <v>102001005</v>
       </c>
@@ -24850,7 +24838,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="23">
         <v>102001006</v>
       </c>
@@ -24894,7 +24882,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="23">
         <v>102001007</v>
       </c>
@@ -24938,7 +24926,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="21">
         <v>103001001</v>
       </c>
@@ -24982,7 +24970,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="21">
         <v>103001002</v>
       </c>
@@ -25026,7 +25014,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="21">
         <v>103001003</v>
       </c>
@@ -25070,7 +25058,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="23">
         <v>103001004</v>
       </c>
@@ -25114,7 +25102,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="23">
         <v>103001005</v>
       </c>
@@ -25158,7 +25146,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="23">
         <v>103001006</v>
       </c>
@@ -25202,7 +25190,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="23">
         <v>103001007</v>
       </c>
@@ -25246,7 +25234,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="21">
         <v>104001001</v>
       </c>
@@ -25290,7 +25278,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="21">
         <v>104001002</v>
       </c>
@@ -25334,7 +25322,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="21">
         <v>104001003</v>
       </c>
@@ -25378,7 +25366,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="23">
         <v>104001004</v>
       </c>
@@ -25422,7 +25410,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="23">
         <v>104001005</v>
       </c>
@@ -25466,7 +25454,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="30" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="23">
         <v>104001006</v>
       </c>
@@ -25510,7 +25498,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="31" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="23">
         <v>104001007</v>
       </c>
@@ -25554,7 +25542,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="21">
         <v>103003003</v>
       </c>
@@ -25598,7 +25586,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="21">
         <v>103003004</v>
       </c>
@@ -25642,7 +25630,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="21">
         <v>103003005</v>
       </c>
@@ -25686,7 +25674,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:14" s="43" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" s="43" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="47">
         <v>104003003</v>
       </c>
@@ -25730,7 +25718,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:14" s="43" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" s="43" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="47">
         <v>104003004</v>
       </c>
@@ -25774,7 +25762,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:14" s="43" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" s="43" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A37" s="47">
         <v>104003005</v>
       </c>
@@ -25818,7 +25806,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:14" s="43" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" s="43" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A38" s="48">
         <v>102003003</v>
       </c>
@@ -25862,7 +25850,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:14" s="43" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" s="43" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A39" s="48">
         <v>102003004</v>
       </c>
@@ -25906,7 +25894,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:14" s="43" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" s="43" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A40" s="48">
         <v>102003005</v>
       </c>
@@ -25950,7 +25938,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:14" s="43" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14" s="43" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="47" t="s">
         <v>335</v>
       </c>
@@ -25994,7 +25982,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:14" s="43" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14" s="43" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="47" t="s">
         <v>339</v>
       </c>
@@ -26038,7 +26026,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:14" s="43" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14" s="43" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="47" t="s">
         <v>342</v>
       </c>
@@ -26082,7 +26070,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="11">
         <v>101002001</v>
       </c>
@@ -26096,7 +26084,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="11">
         <v>101002002</v>
       </c>
@@ -26110,7 +26098,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="11">
         <v>101002003</v>
       </c>
@@ -26124,7 +26112,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="11">
         <v>101002004</v>
       </c>
@@ -26138,7 +26126,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="11">
         <v>101002005</v>
       </c>
@@ -26149,10 +26137,10 @@
         <v>251</v>
       </c>
       <c r="K48" s="25" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="11">
         <v>102002001</v>
       </c>
@@ -26166,7 +26154,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="11">
         <v>102002002</v>
       </c>
@@ -26180,7 +26168,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="11">
         <v>102002003</v>
       </c>
@@ -26194,7 +26182,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="11">
         <v>102002004</v>
       </c>
@@ -26208,7 +26196,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="11">
         <v>102002005</v>
       </c>
@@ -26222,7 +26210,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="11">
         <v>103002001</v>
       </c>
@@ -26236,7 +26224,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="11">
         <v>103002002</v>
       </c>
@@ -26250,7 +26238,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="11">
         <v>103002003</v>
       </c>
@@ -26264,7 +26252,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="11">
         <v>103002004</v>
       </c>
@@ -26278,7 +26266,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="11">
         <v>103002005</v>
       </c>
@@ -26292,7 +26280,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="11">
         <v>104002001</v>
       </c>
@@ -26306,7 +26294,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="11">
         <v>104002002</v>
       </c>
@@ -26320,7 +26308,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="11">
         <v>104002003</v>
       </c>
@@ -26334,7 +26322,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="11">
         <v>104002004</v>
       </c>
@@ -26348,7 +26336,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="11">
         <v>104002005</v>
       </c>
@@ -26362,7 +26350,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>101002006</v>
       </c>
@@ -26376,7 +26364,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="11">
         <v>101002007</v>
       </c>
@@ -26390,7 +26378,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="11">
         <v>104002007</v>
       </c>
@@ -26404,66 +26392,66 @@
         <v>295</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" s="11"/>
       <c r="K67"/>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" s="11"/>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="11"/>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" s="11"/>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" s="11"/>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" s="11"/>
       <c r="K72"/>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" s="11"/>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" s="11"/>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" s="11"/>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" s="11"/>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" s="11"/>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" s="11"/>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" s="11"/>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" s="11"/>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" s="11"/>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" s="11"/>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" s="11"/>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" s="11"/>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" s="11"/>
     </row>
-    <row r="86" spans="1:1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="11"/>
     </row>
   </sheetData>
@@ -26471,80 +26459,78 @@
   <conditionalFormatting sqref="A1">
     <cfRule type="duplicateValues" dxfId="33" priority="33"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A4:A17">
+    <cfRule type="duplicateValues" dxfId="32" priority="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18:A31">
+    <cfRule type="duplicateValues" dxfId="31" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="61"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A32:A34">
+    <cfRule type="duplicateValues" dxfId="29" priority="64"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A35:A37">
+    <cfRule type="duplicateValues" dxfId="28" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A38:A40">
+    <cfRule type="duplicateValues" dxfId="26" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A41:A43">
+    <cfRule type="duplicateValues" dxfId="25" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A44:A63">
+    <cfRule type="duplicateValues" dxfId="24" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="23"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A64">
-    <cfRule type="duplicateValues" dxfId="32" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A65">
-    <cfRule type="duplicateValues" dxfId="29" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A66">
-    <cfRule type="duplicateValues" dxfId="26" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:A17">
-    <cfRule type="duplicateValues" dxfId="23" priority="50"/>
+  <conditionalFormatting sqref="A87:A1048576 A2:A34">
+    <cfRule type="duplicateValues" dxfId="12" priority="34"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A18:A31">
-    <cfRule type="duplicateValues" dxfId="22" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="61"/>
+  <conditionalFormatting sqref="B38:B40">
+    <cfRule type="duplicateValues" dxfId="11" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A32:A34">
-    <cfRule type="duplicateValues" dxfId="20" priority="64"/>
+  <conditionalFormatting sqref="G4:G10">
+    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A44:A63">
-    <cfRule type="duplicateValues" dxfId="19" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="23"/>
+  <conditionalFormatting sqref="G11:G17">
+    <cfRule type="duplicateValues" dxfId="8" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11:G34">
-    <cfRule type="duplicateValues" dxfId="16" priority="66"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G11:G17">
-    <cfRule type="duplicateValues" dxfId="15" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G18:G31">
-    <cfRule type="duplicateValues" dxfId="14" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G32:G34">
-    <cfRule type="duplicateValues" dxfId="12" priority="65"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A87:A1048576 A2:A34">
-    <cfRule type="duplicateValues" dxfId="11" priority="34"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A35:A37">
-    <cfRule type="duplicateValues" dxfId="10" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G35:G37">
-    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G38:G40">
-    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A38:A40">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B38:B40">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G41:G43">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A41:A43">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G10">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G10">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation showInputMessage="1" showErrorMessage="1" sqref="G32:G43 A32:A43 A4:A17 G4:G17" xr:uid="{00000000-0002-0000-0700-000001000000}"/>
@@ -26558,23 +26544,23 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:G72"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.75" style="35" customWidth="1"/>
-    <col min="2" max="2" width="11.375" style="35" customWidth="1"/>
-    <col min="3" max="3" width="13.625" style="35" customWidth="1"/>
-    <col min="4" max="4" width="17.125" style="36" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" style="35" customWidth="1"/>
+    <col min="3" max="3" width="13.58203125" style="35" customWidth="1"/>
+    <col min="4" max="4" width="17.08203125" style="36" customWidth="1"/>
     <col min="5" max="5" width="9" style="35" customWidth="1"/>
     <col min="6" max="16384" width="9" style="35"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>365</v>
       </c>
       <c r="D1" s="30"/>
     </row>
-    <row r="2" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" s="31" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="31" t="s">
         <v>366</v>
       </c>
@@ -26588,7 +26574,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="33" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" s="33" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="33" t="s">
         <v>104</v>
       </c>
@@ -26602,7 +26588,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="35">
         <v>101</v>
       </c>
@@ -26626,7 +26612,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>101</v>
       </c>
@@ -26650,7 +26636,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="35">
         <v>101</v>
       </c>
@@ -26674,7 +26660,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="35">
         <v>102</v>
       </c>
@@ -26698,7 +26684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="35">
         <v>102</v>
       </c>
@@ -26722,7 +26708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="35">
         <v>102</v>
       </c>
@@ -26746,7 +26732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>101</v>
       </c>
@@ -26770,7 +26756,7 @@
         <v>-13.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="35">
         <v>101</v>
       </c>
@@ -26794,7 +26780,7 @@
         <v>-13.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="35">
         <v>101</v>
       </c>
@@ -26818,7 +26804,7 @@
         <v>-13.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="35">
         <v>101</v>
       </c>
@@ -26842,7 +26828,7 @@
         <v>-13.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="35">
         <v>101</v>
       </c>
@@ -26866,7 +26852,7 @@
         <v>-13.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="35">
         <v>101</v>
       </c>
@@ -26890,7 +26876,7 @@
         <v>-13.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="35">
         <v>101</v>
       </c>
@@ -26914,7 +26900,7 @@
         <v>-13.5</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="35">
         <v>101</v>
       </c>
@@ -26938,7 +26924,7 @@
         <v>-11</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="35">
         <v>101</v>
       </c>
@@ -26962,7 +26948,7 @@
         <v>-11</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="35">
         <v>101</v>
       </c>
@@ -26986,7 +26972,7 @@
         <v>-11</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="35">
         <v>101</v>
       </c>
@@ -27010,7 +26996,7 @@
         <v>-11</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="35">
         <v>101</v>
       </c>
@@ -27034,7 +27020,7 @@
         <v>-11</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="35">
         <v>101</v>
       </c>
@@ -27058,7 +27044,7 @@
         <v>-11</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="35">
         <v>101</v>
       </c>
@@ -27082,7 +27068,7 @@
         <v>-11</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="35">
         <v>101</v>
       </c>
@@ -27106,7 +27092,7 @@
         <v>-8.5</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="35">
         <v>101</v>
       </c>
@@ -27130,7 +27116,7 @@
         <v>-8.5</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="35">
         <v>101</v>
       </c>
@@ -27154,7 +27140,7 @@
         <v>-8.5</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="35">
         <v>101</v>
       </c>
@@ -27178,7 +27164,7 @@
         <v>-8.5</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="35">
         <v>101</v>
       </c>
@@ -27202,7 +27188,7 @@
         <v>-8.5</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="35">
         <v>101</v>
       </c>
@@ -27226,7 +27212,7 @@
         <v>-8.5</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="35">
         <v>101</v>
       </c>
@@ -27250,7 +27236,7 @@
         <v>-8.5</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="35">
         <v>101</v>
       </c>
@@ -27274,7 +27260,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="35">
         <v>101</v>
       </c>
@@ -27298,7 +27284,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="35">
         <v>101</v>
       </c>
@@ -27322,7 +27308,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="35">
         <v>101</v>
       </c>
@@ -27346,7 +27332,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="35">
         <v>101</v>
       </c>
@@ -27370,7 +27356,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="35">
         <v>101</v>
       </c>
@@ -27394,7 +27380,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="35">
         <v>101</v>
       </c>
@@ -27418,7 +27404,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="35">
         <v>102</v>
       </c>
@@ -27442,7 +27428,7 @@
         <v>-2.5</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="35">
         <v>102</v>
       </c>
@@ -27466,7 +27452,7 @@
         <v>-2.5</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="35">
         <v>102</v>
       </c>
@@ -27490,7 +27476,7 @@
         <v>-2.5</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="35">
         <v>102</v>
       </c>
@@ -27514,7 +27500,7 @@
         <v>-2.5</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="35">
         <v>102</v>
       </c>
@@ -27538,7 +27524,7 @@
         <v>-2.5</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="35">
         <v>102</v>
       </c>
@@ -27562,7 +27548,7 @@
         <v>-2.5</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="35">
         <v>102</v>
       </c>
@@ -27586,7 +27572,7 @@
         <v>-2.5</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="35">
         <v>102</v>
       </c>
@@ -27610,7 +27596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="35">
         <v>102</v>
       </c>
@@ -27634,7 +27620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="35">
         <v>102</v>
       </c>
@@ -27658,7 +27644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="35">
         <v>102</v>
       </c>
@@ -27682,7 +27668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="35">
         <v>102</v>
       </c>
@@ -27706,7 +27692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="35">
         <v>102</v>
       </c>
@@ -27730,7 +27716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="35">
         <v>102</v>
       </c>
@@ -27754,7 +27740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="35">
         <v>102</v>
       </c>
@@ -27778,7 +27764,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="35">
         <v>102</v>
       </c>
@@ -27802,7 +27788,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="35">
         <v>102</v>
       </c>
@@ -27826,7 +27812,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="35">
         <v>102</v>
       </c>
@@ -27850,7 +27836,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="35">
         <v>102</v>
       </c>
@@ -27874,7 +27860,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="35">
         <v>102</v>
       </c>
@@ -27898,7 +27884,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="35">
         <v>102</v>
       </c>
@@ -27922,7 +27908,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="35">
         <v>102</v>
       </c>
@@ -27946,7 +27932,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="35">
         <v>102</v>
       </c>
@@ -27970,7 +27956,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="35">
         <v>102</v>
       </c>
@@ -27994,7 +27980,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="35">
         <v>102</v>
       </c>
@@ -28018,7 +28004,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="35">
         <v>102</v>
       </c>
@@ -28042,7 +28028,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="35">
         <v>102</v>
       </c>
@@ -28066,7 +28052,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="35">
         <v>102</v>
       </c>
@@ -28090,7 +28076,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="35">
         <v>102</v>
       </c>
@@ -28114,7 +28100,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="35">
         <v>102</v>
       </c>
@@ -28138,7 +28124,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="35">
         <v>102</v>
       </c>
@@ -28162,7 +28148,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="35">
         <v>102</v>
       </c>
@@ -28186,7 +28172,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="35">
         <v>102</v>
       </c>
@@ -28210,7 +28196,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="35">
         <v>102</v>
       </c>
@@ -28234,7 +28220,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="35">
         <v>102</v>
       </c>
